--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2674,284 +2674,6 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>122377554</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Övre Kullåssätern, Vrm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>398029</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6697894</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Norra Ny</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark of dead wood</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Jesper Granback</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Jesper Granback</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>122377425</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57527</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Övre Kullåssätern, Vrm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>398015</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6697901</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Norra Ny</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Jesper Granback</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Jesper Granback</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2674,6 +2674,284 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122377425</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>397978</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6697920</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122377554</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>398006</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6697903</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark of dead wood</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122377425</v>
+        <v>122377554</v>
       </c>
       <c r="B20" t="n">
-        <v>57631</v>
+        <v>79850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,46 +2692,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397978</v>
+        <v>398006</v>
       </c>
       <c r="R20" t="n">
-        <v>6697920</v>
+        <v>6697903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,6 +2781,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2793,6 +2793,16 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2810,10 +2820,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122377554</v>
+        <v>122377425</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,45 +2836,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398006</v>
+        <v>397978</v>
       </c>
       <c r="R21" t="n">
-        <v>6697903</v>
+        <v>6697920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,7 +2926,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2927,16 +2937,6 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122377554</v>
+        <v>122377425</v>
       </c>
       <c r="B20" t="n">
-        <v>79850</v>
+        <v>57634</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,45 +2692,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398006</v>
+        <v>397978</v>
       </c>
       <c r="R20" t="n">
-        <v>6697903</v>
+        <v>6697920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2782,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2793,16 +2793,6 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2820,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122377425</v>
+        <v>122377554</v>
       </c>
       <c r="B21" t="n">
-        <v>57634</v>
+        <v>79852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,46 +2826,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397978</v>
+        <v>398006</v>
       </c>
       <c r="R21" t="n">
-        <v>6697920</v>
+        <v>6697903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2926,6 +2915,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2937,6 +2927,16 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2813,7 +2813,7 @@
         <v>122377554</v>
       </c>
       <c r="B21" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122377554</v>
+        <v>122377425</v>
       </c>
       <c r="B20" t="n">
-        <v>79856</v>
+        <v>57640</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,45 +2692,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>398006</v>
+        <v>397978</v>
       </c>
       <c r="R20" t="n">
-        <v>6697903</v>
+        <v>6697920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2782,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2793,16 +2793,6 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2820,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122377425</v>
+        <v>122377554</v>
       </c>
       <c r="B21" t="n">
-        <v>57634</v>
+        <v>79862</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,46 +2826,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397978</v>
+        <v>398006</v>
       </c>
       <c r="R21" t="n">
-        <v>6697920</v>
+        <v>6697903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2926,6 +2915,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2937,6 +2927,16 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>122377425</v>
       </c>
       <c r="B20" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>122377554</v>
       </c>
       <c r="B21" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2679,7 +2679,7 @@
         <v>122377425</v>
       </c>
       <c r="B20" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>122377554</v>
       </c>
       <c r="B21" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122377425</v>
+        <v>122377554</v>
       </c>
       <c r="B20" t="n">
-        <v>57644</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,46 +2692,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397978</v>
+        <v>398006</v>
       </c>
       <c r="R20" t="n">
-        <v>6697920</v>
+        <v>6697903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,6 +2781,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2793,6 +2793,16 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2810,10 +2820,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122377554</v>
+        <v>122377425</v>
       </c>
       <c r="B21" t="n">
-        <v>79869</v>
+        <v>57644</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,45 +2836,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>398006</v>
+        <v>397978</v>
       </c>
       <c r="R21" t="n">
-        <v>6697903</v>
+        <v>6697920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,7 +2926,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2927,16 +2937,6 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Blandskiktad olikåldrad med huvudsakligen gran, tall o björk.</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark of dead wood</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2952,6 +2952,588 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125419877</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>397978</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6697920</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket garnlav här o var på tallarna.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125419081</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74840</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>397978</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6697920</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125420150</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>398029</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6697894</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125425784</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>398029</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6697894</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125420220</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Övre Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>398029</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6697894</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125419877</v>
+        <v>125425784</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2970,37 +2970,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397978</v>
+        <v>398029</v>
       </c>
       <c r="R22" t="n">
-        <v>6697920</v>
+        <v>6697894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,12 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket garnlav här o var på tallarna.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,7 +3048,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3075,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125419081</v>
+        <v>125418955</v>
       </c>
       <c r="B23" t="n">
-        <v>74840</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,31 +3078,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
@@ -3153,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3163,12 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,7 +3160,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3308,10 +3290,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125425784</v>
+        <v>125420220</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3324,24 +3306,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
@@ -3383,7 +3368,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3393,7 +3378,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,6 +3387,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3420,10 +3406,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125420220</v>
+        <v>125419081</v>
       </c>
       <c r="B26" t="n">
-        <v>78546</v>
+        <v>74840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,25 +3418,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3463,10 +3449,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>398029</v>
+        <v>397978</v>
       </c>
       <c r="R26" t="n">
-        <v>6697894</v>
+        <v>6697920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,7 +3484,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,7 +3494,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,6 +3524,937 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125419158</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>397890</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6697937</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125426865</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>397910</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6697934</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125419083</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98018</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>397869</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6697920</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125419996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>398074</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6697878</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125447044</v>
+      </c>
+      <c r="B31" t="n">
+        <v>74840</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kattfotslav, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>397850</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6697918</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125419993</v>
+      </c>
+      <c r="B32" t="n">
+        <v>74840</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>398074</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6697878</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125447089</v>
+      </c>
+      <c r="B33" t="n">
+        <v>74840</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kattfotslav, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>397868</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697902</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125422828</v>
+      </c>
+      <c r="B34" t="n">
+        <v>74840</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>398834</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6697963</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2954,10 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125425784</v>
+        <v>125418813</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>398029</v>
+        <v>397978</v>
       </c>
       <c r="R22" t="n">
-        <v>6697894</v>
+        <v>6697920</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125418955</v>
+        <v>125420150</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397978</v>
+        <v>398029</v>
       </c>
       <c r="R23" t="n">
-        <v>6697920</v>
+        <v>6697894</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125420150</v>
+        <v>125420220</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3194,24 +3194,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
@@ -3253,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3263,7 +3266,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3272,6 +3275,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3290,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125420220</v>
+        <v>125419081</v>
       </c>
       <c r="B25" t="n">
-        <v>78546</v>
+        <v>74964</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,25 +3306,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3333,10 +3337,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398029</v>
+        <v>397978</v>
       </c>
       <c r="R25" t="n">
-        <v>6697894</v>
+        <v>6697920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3368,7 +3372,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,7 +3382,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125419081</v>
+        <v>125425784</v>
       </c>
       <c r="B26" t="n">
-        <v>74840</v>
+        <v>78684</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3418,41 +3427,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>397978</v>
+        <v>398029</v>
       </c>
       <c r="R26" t="n">
-        <v>6697920</v>
+        <v>6697894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3484,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3494,12 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3508,7 +3509,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3527,10 +3527,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125419158</v>
+        <v>125447044</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>74964</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,49 +3539,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kattfotslav, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397890</v>
+        <v>397850</v>
       </c>
       <c r="R27" t="n">
-        <v>6697937</v>
+        <v>6697918</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3610,7 +3605,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3620,7 +3615,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3629,6 +3624,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3647,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125426865</v>
+        <v>125419993</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>74964</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3659,55 +3655,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397910</v>
+        <v>398074</v>
       </c>
       <c r="R28" t="n">
-        <v>6697934</v>
+        <v>6697878</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3736,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3746,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B29" t="n">
-        <v>98018</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3785,31 +3767,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3817,13 +3803,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R29" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3852,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3862,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3871,7 +3857,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3890,10 +3875,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419996</v>
+        <v>125447089</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>74964</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3902,38 +3887,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kattfotslav, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>398074</v>
+        <v>397868</v>
       </c>
       <c r="R30" t="n">
-        <v>6697878</v>
+        <v>6697902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3953,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3963,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,6 +3972,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4002,10 +3991,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125447044</v>
+        <v>125419083</v>
       </c>
       <c r="B31" t="n">
-        <v>74840</v>
+        <v>98186</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4018,40 +4007,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kattfotslav, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397850</v>
+        <v>397869</v>
       </c>
       <c r="R31" t="n">
-        <v>6697918</v>
+        <v>6697920</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4080,7 +4070,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4090,7 +4080,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,10 +4108,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125419993</v>
+        <v>125419996</v>
       </c>
       <c r="B32" t="n">
-        <v>74840</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4130,25 +4120,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4164,7 +4154,7 @@
         <v>6697878</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4230,10 +4220,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125447089</v>
+        <v>125422828</v>
       </c>
       <c r="B33" t="n">
-        <v>74840</v>
+        <v>74964</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4264,19 +4254,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kattfotslav, Vrm</t>
+          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397868</v>
+        <v>398834</v>
       </c>
       <c r="R33" t="n">
-        <v>6697902</v>
+        <v>6697963</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4308,7 +4295,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4318,7 +4305,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4327,7 +4314,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4346,10 +4332,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125422828</v>
+        <v>125426865</v>
       </c>
       <c r="B34" t="n">
-        <v>74840</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4358,38 +4344,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398834</v>
+        <v>397910</v>
       </c>
       <c r="R34" t="n">
-        <v>6697963</v>
+        <v>6697934</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2954,7 +2954,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125418813</v>
+        <v>125420150</v>
       </c>
       <c r="B22" t="n">
         <v>78947</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397978</v>
+        <v>398029</v>
       </c>
       <c r="R22" t="n">
-        <v>6697920</v>
+        <v>6697894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,7 +3066,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125420150</v>
+        <v>125419877</v>
       </c>
       <c r="B23" t="n">
         <v>78947</v>
@@ -3100,16 +3100,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>398029</v>
+        <v>397978</v>
       </c>
       <c r="R23" t="n">
-        <v>6697894</v>
+        <v>6697920</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3154,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket garnlav här o var på tallarna.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,6 +3168,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3178,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125420220</v>
+        <v>125419081</v>
       </c>
       <c r="B24" t="n">
-        <v>78683</v>
+        <v>74964</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,25 +3199,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3221,10 +3230,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>398029</v>
+        <v>397978</v>
       </c>
       <c r="R24" t="n">
-        <v>6697894</v>
+        <v>6697920</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3266,7 +3275,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,10 +3308,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125419081</v>
+        <v>125420220</v>
       </c>
       <c r="B25" t="n">
-        <v>74964</v>
+        <v>78683</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,25 +3320,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3337,10 +3351,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397978</v>
+        <v>398029</v>
       </c>
       <c r="R25" t="n">
-        <v>6697920</v>
+        <v>6697894</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3386,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3382,12 +3396,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,10 +3536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125447044</v>
+        <v>125419996</v>
       </c>
       <c r="B27" t="n">
-        <v>74964</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,41 +3548,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kattfotslav, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397850</v>
+        <v>398074</v>
       </c>
       <c r="R27" t="n">
-        <v>6697918</v>
+        <v>6697878</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3605,7 +3611,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3615,7 +3621,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,7 +3630,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3643,7 +3648,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125419993</v>
+        <v>125447089</v>
       </c>
       <c r="B28" t="n">
         <v>74964</v>
@@ -3677,19 +3682,22 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kattfotslav, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>398074</v>
+        <v>397868</v>
       </c>
       <c r="R28" t="n">
-        <v>6697878</v>
+        <v>6697902</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3718,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3737,6 +3745,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3755,10 +3764,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125419158</v>
+        <v>125419993</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
+        <v>74964</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3767,49 +3776,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397890</v>
+        <v>398074</v>
       </c>
       <c r="R29" t="n">
-        <v>6697937</v>
+        <v>6697878</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3838,7 +3839,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3849,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,10 +3876,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125447089</v>
+        <v>125419158</v>
       </c>
       <c r="B30" t="n">
-        <v>74964</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3887,44 +3888,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kattfotslav, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397868</v>
+        <v>397890</v>
       </c>
       <c r="R30" t="n">
-        <v>6697902</v>
+        <v>6697937</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3953,7 +3959,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3963,7 +3969,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3972,7 +3978,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3991,10 +3996,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419083</v>
+        <v>125447044</v>
       </c>
       <c r="B31" t="n">
-        <v>98186</v>
+        <v>74964</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4007,41 +4012,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kattfotslav, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397869</v>
+        <v>397850</v>
       </c>
       <c r="R31" t="n">
-        <v>6697920</v>
+        <v>6697918</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4070,7 +4074,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4080,7 +4084,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4108,10 +4112,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125419996</v>
+        <v>125426865</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4120,38 +4124,52 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>398074</v>
+        <v>397910</v>
       </c>
       <c r="R32" t="n">
-        <v>6697878</v>
+        <v>6697934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,7 +4201,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4193,7 +4211,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,10 +4238,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125422828</v>
+        <v>125419083</v>
       </c>
       <c r="B33" t="n">
-        <v>74964</v>
+        <v>98186</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4236,37 +4254,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>398834</v>
+        <v>397869</v>
       </c>
       <c r="R33" t="n">
-        <v>6697963</v>
+        <v>6697920</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4295,7 +4317,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4305,7 +4327,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4314,6 +4336,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4332,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125426865</v>
+        <v>125422828</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
+        <v>74964</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4344,52 +4367,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>397910</v>
+        <v>398834</v>
       </c>
       <c r="R34" t="n">
-        <v>6697934</v>
+        <v>6697963</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4421,7 +4430,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4431,7 +4440,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4465,6 +4465,3546 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125698310</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43932</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>398204</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6697895</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125700176</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>398044</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6697944</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125700268</v>
+      </c>
+      <c r="B37" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>398012</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6697933</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125698508</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>398307</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6697923</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125700564</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79033</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>397969</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6697932</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125696949</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>397918</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6697928</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125698646</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43932</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>398341</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6697940</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125699719</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>398265</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6697945</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125698845</v>
+      </c>
+      <c r="B43" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>398355</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6697919</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125698599</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>398320</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6697905</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125700296</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>397992</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6697940</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125700228</v>
+      </c>
+      <c r="B46" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>398025</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6697933</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125698359</v>
+      </c>
+      <c r="B47" t="n">
+        <v>43932</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>398223</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6697923</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125697063</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>397935</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6697897</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125700601</v>
+      </c>
+      <c r="B49" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>53</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>397968</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6697927</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125699772</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>398238</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6697953</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125698761</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>398357</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6697925</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125697625</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80900</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>398114</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6697905</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125700356</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>397983</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6697932</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125699923</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>398147</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6697955</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125697120</v>
+      </c>
+      <c r="B55" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>397946</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6697893</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125699868</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>398211</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6697955</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125697246</v>
+      </c>
+      <c r="B57" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>397988</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6697895</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125698905</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>398367</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6697942</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125697394</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>397995</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6697902</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125698527</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>398294</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6697907</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125700252</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>398016</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6697937</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125698710</v>
+      </c>
+      <c r="B62" t="n">
+        <v>43932</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>398341</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6697932</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125697091</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79033</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>397938</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6697903</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125696921</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>397904</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6697885</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125698575</v>
+      </c>
+      <c r="B65" t="n">
+        <v>43932</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>398319</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6697916</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125698253</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>398216</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6697912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125700680</v>
+      </c>
+      <c r="B67" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>397883</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6697899</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125696883</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>397885</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6697905</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,15 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125420150</v>
+        <v>125425784</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,21 +2965,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3029,7 +3024,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3034,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,15 +3061,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125419877</v>
+        <v>125420220</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,21 +3072,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3109,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397978</v>
+        <v>398029</v>
       </c>
       <c r="R23" t="n">
-        <v>6697920</v>
+        <v>6697894</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3144,7 +3134,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3154,12 +3144,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket garnlav här o var på tallarna.</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,43 +3172,35 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125419081</v>
+        <v>125418813</v>
       </c>
       <c r="B24" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Övre Kullåssätern, Vrm</t>
@@ -3265,7 +3242,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3275,12 +3252,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,7 +3261,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3308,37 +3279,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125420220</v>
+        <v>125419081</v>
       </c>
       <c r="B25" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3351,10 +3317,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>398029</v>
+        <v>397978</v>
       </c>
       <c r="R25" t="n">
-        <v>6697894</v>
+        <v>6697920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3386,7 +3352,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3396,7 +3362,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,15 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125425784</v>
+        <v>125423621</v>
       </c>
       <c r="B26" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,21 +3406,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3499,7 +3465,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3509,7 +3475,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3536,50 +3502,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125419996</v>
+        <v>125422828</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>398074</v>
+        <v>398834</v>
       </c>
       <c r="R27" t="n">
-        <v>6697878</v>
+        <v>6697963</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3611,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3621,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,15 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125447089</v>
+        <v>125419993</v>
       </c>
       <c r="B28" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3682,22 +3638,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kattfotslav, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397868</v>
+        <v>398074</v>
       </c>
       <c r="R28" t="n">
-        <v>6697902</v>
+        <v>6697878</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3745,7 +3698,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3764,53 +3716,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125419993</v>
+        <v>125426865</v>
       </c>
       <c r="B29" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>398074</v>
+        <v>397910</v>
       </c>
       <c r="R29" t="n">
-        <v>6697878</v>
+        <v>6697934</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3839,7 +3800,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3849,7 +3810,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3879,12 +3840,7 @@
         <v>125419158</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3996,15 +3952,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125447044</v>
+        <v>125419083</v>
       </c>
       <c r="B31" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4012,40 +3963,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kattfotslav, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397850</v>
+        <v>397869</v>
       </c>
       <c r="R31" t="n">
-        <v>6697918</v>
+        <v>6697920</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4074,7 +4026,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4036,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4112,64 +4064,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125426865</v>
+        <v>125419996</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>397910</v>
+        <v>398074</v>
       </c>
       <c r="R32" t="n">
-        <v>6697934</v>
+        <v>6697878</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4201,7 +4134,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4211,7 +4144,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4238,15 +4171,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125419083</v>
+        <v>125447089</v>
       </c>
       <c r="B33" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,41 +4182,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kattfotslav, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397869</v>
+        <v>397868</v>
       </c>
       <c r="R33" t="n">
-        <v>6697920</v>
+        <v>6697902</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4317,7 +4244,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4327,7 +4254,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,15 +4282,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125422828</v>
+        <v>125447044</v>
       </c>
       <c r="B34" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,16 +4311,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Övre  Kullåssätern, Övre  Kullåssätern, Vrm</t>
+          <t>Kattfotslav, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>398834</v>
+        <v>397850</v>
       </c>
       <c r="R34" t="n">
-        <v>6697963</v>
+        <v>6697918</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4430,7 +4355,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4440,7 +4365,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4449,6 +4374,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4467,15 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698310</v>
+        <v>125698845</v>
       </c>
       <c r="B35" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4483,39 +4404,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398204</v>
+        <v>398355</v>
       </c>
       <c r="R35" t="n">
-        <v>6697895</v>
+        <v>6697919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4574,15 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700176</v>
+        <v>125700228</v>
       </c>
       <c r="B36" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4610,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398044</v>
+        <v>398025</v>
       </c>
       <c r="R36" t="n">
-        <v>6697944</v>
+        <v>6697933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4676,15 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125700268</v>
+        <v>125698646</v>
       </c>
       <c r="B37" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,34 +4598,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>398012</v>
+        <v>398341</v>
       </c>
       <c r="R37" t="n">
-        <v>6697933</v>
+        <v>6697940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4778,50 +4689,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125698508</v>
+        <v>125698575</v>
       </c>
       <c r="B38" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>398307</v>
+        <v>398319</v>
       </c>
       <c r="R38" t="n">
-        <v>6697923</v>
+        <v>6697916</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4880,50 +4791,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125700564</v>
+        <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>79033</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397969</v>
+        <v>398216</v>
       </c>
       <c r="R39" t="n">
-        <v>6697932</v>
+        <v>6697912</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4966,26 +4872,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5002,50 +4888,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125696949</v>
+        <v>125698359</v>
       </c>
       <c r="B40" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>101735</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397918</v>
+        <v>398223</v>
       </c>
       <c r="R40" t="n">
-        <v>6697928</v>
+        <v>6697923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5104,55 +4990,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125698646</v>
+        <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398341</v>
+        <v>397968</v>
       </c>
       <c r="R41" t="n">
-        <v>6697940</v>
+        <v>6697927</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5211,15 +5087,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699719</v>
+        <v>125700252</v>
       </c>
       <c r="B42" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,14 +5118,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>398265</v>
+        <v>398016</v>
       </c>
       <c r="R42" t="n">
-        <v>6697945</v>
+        <v>6697937</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5313,50 +5184,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125698845</v>
+        <v>125696883</v>
       </c>
       <c r="B43" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>398355</v>
+        <v>397885</v>
       </c>
       <c r="R43" t="n">
-        <v>6697919</v>
+        <v>6697905</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5415,15 +5281,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125698599</v>
+        <v>125699772</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,10 +5316,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398320</v>
+        <v>398238</v>
       </c>
       <c r="R44" t="n">
-        <v>6697905</v>
+        <v>6697953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5517,37 +5378,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125700296</v>
+        <v>125700268</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5557,10 +5413,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397992</v>
+        <v>398012</v>
       </c>
       <c r="R45" t="n">
-        <v>6697940</v>
+        <v>6697933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5619,50 +5475,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125700228</v>
+        <v>125698599</v>
       </c>
       <c r="B46" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398025</v>
+        <v>398320</v>
       </c>
       <c r="R46" t="n">
-        <v>6697933</v>
+        <v>6697905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5721,15 +5572,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125698359</v>
+        <v>125697091</v>
       </c>
       <c r="B47" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79053</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5737,39 +5583,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101735</v>
+        <v>6450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398223</v>
+        <v>397938</v>
       </c>
       <c r="R47" t="n">
-        <v>6697923</v>
+        <v>6697903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,59 +5669,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125697063</v>
+        <v>125698761</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397935</v>
+        <v>398357</v>
       </c>
       <c r="R48" t="n">
-        <v>6697897</v>
+        <v>6697925</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5939,15 +5766,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125700601</v>
+        <v>125700296</v>
       </c>
       <c r="B49" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5955,21 +5777,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5979,10 +5801,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397968</v>
+        <v>397992</v>
       </c>
       <c r="R49" t="n">
-        <v>6697927</v>
+        <v>6697940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6041,50 +5863,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125699772</v>
+        <v>125700564</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398238</v>
+        <v>397969</v>
       </c>
       <c r="R50" t="n">
-        <v>6697953</v>
+        <v>6697932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6127,6 +5944,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6143,50 +5980,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125698761</v>
+        <v>125699923</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398357</v>
+        <v>398147</v>
       </c>
       <c r="R51" t="n">
-        <v>6697925</v>
+        <v>6697955</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6245,15 +6086,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125697625</v>
+        <v>125699719</v>
       </c>
       <c r="B52" t="n">
-        <v>80900</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6261,21 +6097,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6285,10 +6121,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>398114</v>
+        <v>398265</v>
       </c>
       <c r="R52" t="n">
-        <v>6697905</v>
+        <v>6697945</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6347,37 +6183,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125700356</v>
+        <v>125697120</v>
       </c>
       <c r="B53" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6387,10 +6218,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>397983</v>
+        <v>397946</v>
       </c>
       <c r="R53" t="n">
-        <v>6697932</v>
+        <v>6697893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6449,59 +6280,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125699923</v>
+        <v>125700356</v>
       </c>
       <c r="B54" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>398147</v>
+        <v>397983</v>
       </c>
       <c r="R54" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6560,15 +6377,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125697120</v>
+        <v>125697246</v>
       </c>
       <c r="B55" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6600,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397946</v>
+        <v>397988</v>
       </c>
       <c r="R55" t="n">
-        <v>6697893</v>
+        <v>6697895</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6662,15 +6474,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125699868</v>
+        <v>125697625</v>
       </c>
       <c r="B56" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80942</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6678,21 +6485,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6702,10 +6509,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>398211</v>
+        <v>398114</v>
       </c>
       <c r="R56" t="n">
-        <v>6697955</v>
+        <v>6697905</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6764,37 +6571,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125697246</v>
+        <v>125696949</v>
       </c>
       <c r="B57" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6804,10 +6606,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>397988</v>
+        <v>397918</v>
       </c>
       <c r="R57" t="n">
-        <v>6697895</v>
+        <v>6697928</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6866,50 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125698905</v>
+        <v>125700680</v>
       </c>
       <c r="B58" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398367</v>
+        <v>397883</v>
       </c>
       <c r="R58" t="n">
-        <v>6697942</v>
+        <v>6697899</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6968,50 +6765,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125697394</v>
+        <v>125696921</v>
       </c>
       <c r="B59" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>397995</v>
+        <v>397904</v>
       </c>
       <c r="R59" t="n">
-        <v>6697902</v>
+        <v>6697885</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7070,15 +6871,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125698527</v>
+        <v>125699868</v>
       </c>
       <c r="B60" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7110,10 +6906,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398294</v>
+        <v>398211</v>
       </c>
       <c r="R60" t="n">
-        <v>6697907</v>
+        <v>6697955</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7172,15 +6968,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125700252</v>
+        <v>125698905</v>
       </c>
       <c r="B61" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7208,14 +6999,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398016</v>
+        <v>398367</v>
       </c>
       <c r="R61" t="n">
-        <v>6697937</v>
+        <v>6697942</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7274,15 +7065,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125698710</v>
+        <v>125698310</v>
       </c>
       <c r="B62" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7319,10 +7105,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398341</v>
+        <v>398204</v>
       </c>
       <c r="R62" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7381,15 +7167,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125697091</v>
+        <v>125698710</v>
       </c>
       <c r="B63" t="n">
-        <v>79033</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7397,34 +7178,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6450</v>
+        <v>101735</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>397938</v>
+        <v>398341</v>
       </c>
       <c r="R63" t="n">
-        <v>6697903</v>
+        <v>6697932</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7483,15 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125696921</v>
+        <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7518,7 +7299,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7532,10 +7313,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>397904</v>
+        <v>397935</v>
       </c>
       <c r="R64" t="n">
-        <v>6697885</v>
+        <v>6697897</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7594,55 +7375,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125698575</v>
+        <v>125697394</v>
       </c>
       <c r="B65" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398319</v>
+        <v>397995</v>
       </c>
       <c r="R65" t="n">
-        <v>6697916</v>
+        <v>6697902</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7701,37 +7472,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125698253</v>
+        <v>125700176</v>
       </c>
       <c r="B66" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7741,10 +7507,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398216</v>
+        <v>398044</v>
       </c>
       <c r="R66" t="n">
-        <v>6697912</v>
+        <v>6697944</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7803,50 +7569,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125700680</v>
+        <v>125698508</v>
       </c>
       <c r="B67" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>397883</v>
+        <v>398307</v>
       </c>
       <c r="R67" t="n">
-        <v>6697899</v>
+        <v>6697923</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7905,15 +7666,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125696883</v>
+        <v>125698527</v>
       </c>
       <c r="B68" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7941,14 +7697,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>397885</v>
+        <v>398294</v>
       </c>
       <c r="R68" t="n">
-        <v>6697905</v>
+        <v>6697907</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,6 +7760,3395 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125719981</v>
+      </c>
+      <c r="B69" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>397142</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6697816</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125721868</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>397473</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6697852</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125721577</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>397395</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6697867</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125721710</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>397381</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6697850</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125721040</v>
+      </c>
+      <c r="B73" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>397171</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6697871</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125719936</v>
+      </c>
+      <c r="B74" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>53</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>397145</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6697801</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125720225</v>
+      </c>
+      <c r="B75" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>397113</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6697838</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125721492</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>185</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>397334</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6697894</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125720252</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>397108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6697837</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125721012</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>397124</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6697850</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125720843</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>397075</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6697869</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125722033</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>397606</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6697859</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125722105</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>397625</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6697852</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125720079</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>397116</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6697830</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125721614</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>397350</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6697835</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125721536</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>397361</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6697854</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125721835</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80942</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>397433</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6697891</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125722112</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>397625</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6697852</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125720473</v>
+      </c>
+      <c r="B87" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>397024</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6697840</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125721877</v>
+      </c>
+      <c r="B88" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>397502</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6697866</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125720934</v>
+      </c>
+      <c r="B89" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>53</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>397112</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6697860</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125722060</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>397606</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6697859</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125721765</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>397383</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6697865</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125720910</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>397092</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6697872</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125720604</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>396991</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6697837</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125721651</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>397346</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6697842</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>125721224</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>397232</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6697857</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>125721700</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>397397</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6697850</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>125720121</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>397116</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6697806</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>125720782</v>
+      </c>
+      <c r="B98" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>397014</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6697845</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>125720994</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>397124</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6697850</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>125721374</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79585</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>397266</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6697866</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>125720024</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>397180</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6697817</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B35" t="n">
         <v>75005</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R35" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B36" t="n">
         <v>75005</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R36" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125698599</v>
+        <v>125700296</v>
       </c>
       <c r="B46" t="n">
         <v>78967</v>
@@ -5506,14 +5506,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398320</v>
+        <v>397992</v>
       </c>
       <c r="R46" t="n">
-        <v>6697905</v>
+        <v>6697940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5572,45 +5572,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125697091</v>
+        <v>125698599</v>
       </c>
       <c r="B47" t="n">
-        <v>79053</v>
+        <v>78967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397938</v>
+        <v>398320</v>
       </c>
       <c r="R47" t="n">
-        <v>6697903</v>
+        <v>6697905</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,45 +5669,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125698761</v>
+        <v>125697091</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>79053</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398357</v>
+        <v>397938</v>
       </c>
       <c r="R48" t="n">
-        <v>6697925</v>
+        <v>6697903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5766,7 +5766,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125700296</v>
+        <v>125698761</v>
       </c>
       <c r="B49" t="n">
         <v>78967</v>
@@ -5797,14 +5797,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397992</v>
+        <v>398357</v>
       </c>
       <c r="R49" t="n">
-        <v>6697940</v>
+        <v>6697925</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R54" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R55" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6668,45 +6668,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125700680</v>
+        <v>125696921</v>
       </c>
       <c r="B58" t="n">
-        <v>75005</v>
+        <v>98324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>397883</v>
+        <v>397904</v>
       </c>
       <c r="R58" t="n">
-        <v>6697899</v>
+        <v>6697885</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,54 +6774,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125696921</v>
+        <v>125699868</v>
       </c>
       <c r="B59" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>397904</v>
+        <v>398211</v>
       </c>
       <c r="R59" t="n">
-        <v>6697885</v>
+        <v>6697955</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125699868</v>
+        <v>125698905</v>
       </c>
       <c r="B60" t="n">
         <v>78967</v>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398211</v>
+        <v>398367</v>
       </c>
       <c r="R60" t="n">
-        <v>6697955</v>
+        <v>6697942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6968,45 +6968,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125698905</v>
+        <v>125698310</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>43933</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398367</v>
+        <v>398204</v>
       </c>
       <c r="R61" t="n">
-        <v>6697942</v>
+        <v>6697895</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,10 +7070,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125698310</v>
+        <v>125700680</v>
       </c>
       <c r="B62" t="n">
-        <v>43933</v>
+        <v>75005</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7076,39 +7081,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398204</v>
+        <v>397883</v>
       </c>
       <c r="R62" t="n">
-        <v>6697895</v>
+        <v>6697899</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8599,32 +8599,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125720252</v>
+        <v>125721012</v>
       </c>
       <c r="B77" t="n">
-        <v>98324</v>
+        <v>80030</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397108</v>
+        <v>397124</v>
       </c>
       <c r="R77" t="n">
-        <v>6697837</v>
+        <v>6697850</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8696,32 +8696,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721012</v>
+        <v>125720252</v>
       </c>
       <c r="B78" t="n">
-        <v>80030</v>
+        <v>98324</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397124</v>
+        <v>397108</v>
       </c>
       <c r="R78" t="n">
-        <v>6697850</v>
+        <v>6697837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9609,32 +9609,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B87" t="n">
-        <v>75005</v>
+        <v>96577</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R87" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,45 +9706,55 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125721877</v>
+        <v>125722060</v>
       </c>
       <c r="B88" t="n">
-        <v>75005</v>
+        <v>57811</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397502</v>
+        <v>397606</v>
       </c>
       <c r="R88" t="n">
-        <v>6697866</v>
+        <v>6697859</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,32 +9813,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B89" t="n">
-        <v>96577</v>
+        <v>75005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9838,10 +9848,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R89" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9900,55 +9910,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125722060</v>
+        <v>125721877</v>
       </c>
       <c r="B90" t="n">
-        <v>57811</v>
+        <v>75005</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397606</v>
+        <v>397502</v>
       </c>
       <c r="R90" t="n">
-        <v>6697859</v>
+        <v>6697866</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -3719,7 +3719,7 @@
         <v>125426865</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,42 +3837,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419158</v>
+        <v>125419083</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>98248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3880,13 +3876,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397890</v>
+        <v>397869</v>
       </c>
       <c r="R30" t="n">
-        <v>6697937</v>
+        <v>6697920</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3915,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,6 +3930,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3952,38 +3949,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B31" t="n">
-        <v>98241</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3991,13 +3992,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R31" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4026,7 +4027,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4036,7 +4037,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,7 +4046,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B35" t="n">
         <v>75005</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R35" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B36" t="n">
         <v>75005</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R36" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698253</v>
+        <v>125700601</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>96584</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,34 +4802,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398216</v>
+        <v>397968</v>
       </c>
       <c r="R39" t="n">
-        <v>6697912</v>
+        <v>6697927</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4990,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125700601</v>
+        <v>125698253</v>
       </c>
       <c r="B41" t="n">
-        <v>96577</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5001,34 +5001,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397968</v>
+        <v>398216</v>
       </c>
       <c r="R41" t="n">
-        <v>6697927</v>
+        <v>6697912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R44" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B45" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R45" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125700296</v>
+        <v>125698599</v>
       </c>
       <c r="B46" t="n">
         <v>78967</v>
@@ -5506,14 +5506,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>397992</v>
+        <v>398320</v>
       </c>
       <c r="R46" t="n">
-        <v>6697940</v>
+        <v>6697905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5572,45 +5572,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125698599</v>
+        <v>125697091</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>79053</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398320</v>
+        <v>397938</v>
       </c>
       <c r="R47" t="n">
-        <v>6697905</v>
+        <v>6697903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,45 +5669,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125697091</v>
+        <v>125698761</v>
       </c>
       <c r="B48" t="n">
-        <v>79053</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397938</v>
+        <v>398357</v>
       </c>
       <c r="R48" t="n">
-        <v>6697903</v>
+        <v>6697925</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5766,7 +5766,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125698761</v>
+        <v>125700296</v>
       </c>
       <c r="B49" t="n">
         <v>78967</v>
@@ -5797,14 +5797,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398357</v>
+        <v>397992</v>
       </c>
       <c r="R49" t="n">
-        <v>6697925</v>
+        <v>6697940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5863,45 +5863,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125700564</v>
+        <v>125699923</v>
       </c>
       <c r="B50" t="n">
-        <v>79053</v>
+        <v>98331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>397969</v>
+        <v>398147</v>
       </c>
       <c r="R50" t="n">
-        <v>6697932</v>
+        <v>6697955</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,26 +5953,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5980,54 +5969,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125699923</v>
+        <v>125700564</v>
       </c>
       <c r="B51" t="n">
-        <v>98324</v>
+        <v>79053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398147</v>
+        <v>397969</v>
       </c>
       <c r="R51" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6070,6 +6050,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B54" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R54" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R55" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6668,54 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125696921</v>
+        <v>125699868</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>397904</v>
+        <v>398211</v>
       </c>
       <c r="R58" t="n">
-        <v>6697885</v>
+        <v>6697955</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6774,7 +6765,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125699868</v>
+        <v>125698905</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6809,10 +6800,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398211</v>
+        <v>398367</v>
       </c>
       <c r="R59" t="n">
-        <v>6697955</v>
+        <v>6697942</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,45 +6862,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125698905</v>
+        <v>125700680</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398367</v>
+        <v>397883</v>
       </c>
       <c r="R60" t="n">
-        <v>6697942</v>
+        <v>6697899</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7070,45 +7061,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125700680</v>
+        <v>125696921</v>
       </c>
       <c r="B62" t="n">
-        <v>75005</v>
+        <v>98331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>397883</v>
+        <v>397904</v>
       </c>
       <c r="R62" t="n">
-        <v>6697899</v>
+        <v>6697885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B70" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7871,34 +7871,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R70" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,6 +7941,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7957,10 +7977,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B71" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,34 +7988,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R71" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8038,26 +8058,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125719936</v>
+        <v>125720225</v>
       </c>
       <c r="B74" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>397145</v>
+        <v>397113</v>
       </c>
       <c r="R74" t="n">
-        <v>6697801</v>
+        <v>6697838</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8349,26 +8349,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8385,10 +8365,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125720225</v>
+        <v>125719936</v>
       </c>
       <c r="B75" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8420,10 +8400,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397113</v>
+        <v>397145</v>
       </c>
       <c r="R75" t="n">
-        <v>6697838</v>
+        <v>6697801</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8466,6 +8446,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721492</v>
+        <v>125721012</v>
       </c>
       <c r="B76" t="n">
-        <v>78999</v>
+        <v>80030</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397334</v>
+        <v>397124</v>
       </c>
       <c r="R76" t="n">
-        <v>6697894</v>
+        <v>6697850</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,26 +8563,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8599,32 +8579,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721012</v>
+        <v>125721492</v>
       </c>
       <c r="B77" t="n">
-        <v>80030</v>
+        <v>78999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8634,10 +8614,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397124</v>
+        <v>397334</v>
       </c>
       <c r="R77" t="n">
-        <v>6697850</v>
+        <v>6697894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8680,6 +8660,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8699,7 +8699,7 @@
         <v>125720252</v>
       </c>
       <c r="B78" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720079</v>
+        <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>80030</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397116</v>
+        <v>397361</v>
       </c>
       <c r="R82" t="n">
-        <v>6697830</v>
+        <v>6697854</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,26 +9185,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9221,32 +9201,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>78726</v>
+        <v>80030</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R83" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,6 +9282,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R84" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,32 +9609,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B87" t="n">
-        <v>96577</v>
+        <v>75005</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R87" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,55 +9706,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125722060</v>
+        <v>125721877</v>
       </c>
       <c r="B88" t="n">
-        <v>57811</v>
+        <v>75005</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397606</v>
+        <v>397502</v>
       </c>
       <c r="R88" t="n">
-        <v>6697859</v>
+        <v>6697866</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9813,32 +9803,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B89" t="n">
-        <v>75005</v>
+        <v>96584</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9848,10 +9838,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R89" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9910,45 +9900,55 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125721877</v>
+        <v>125722060</v>
       </c>
       <c r="B90" t="n">
-        <v>75005</v>
+        <v>57811</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397502</v>
+        <v>397606</v>
       </c>
       <c r="R90" t="n">
-        <v>6697866</v>
+        <v>6697859</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720994</v>
+        <v>125720024</v>
       </c>
       <c r="B99" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397124</v>
+        <v>397180</v>
       </c>
       <c r="R99" t="n">
-        <v>6697850</v>
+        <v>6697817</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,14 +10894,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10912,46 +10917,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721374</v>
+        <v>125720994</v>
       </c>
       <c r="B100" t="n">
-        <v>79585</v>
+        <v>80070</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10959,21 +10944,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10983,10 +10968,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397266</v>
+        <v>397124</v>
       </c>
       <c r="R100" t="n">
-        <v>6697866</v>
+        <v>6697850</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11021,6 +11006,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11029,6 +11019,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11045,10 +11055,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125720024</v>
+        <v>125721374</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11056,21 +11066,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11080,13 +11090,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397180</v>
+        <v>397266</v>
       </c>
       <c r="R101" t="n">
-        <v>6697817</v>
+        <v>6697866</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11113,19 +11123,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B44" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R44" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R45" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721012</v>
+        <v>125721492</v>
       </c>
       <c r="B76" t="n">
-        <v>80030</v>
+        <v>78999</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397124</v>
+        <v>397334</v>
       </c>
       <c r="R76" t="n">
-        <v>6697850</v>
+        <v>6697894</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,6 +8563,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8579,32 +8599,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8614,10 +8634,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R77" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8660,26 +8680,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8696,32 +8696,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125720252</v>
+        <v>125721012</v>
       </c>
       <c r="B78" t="n">
-        <v>98331</v>
+        <v>80030</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397108</v>
+        <v>397124</v>
       </c>
       <c r="R78" t="n">
-        <v>6697837</v>
+        <v>6697850</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9609,32 +9609,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B87" t="n">
-        <v>75005</v>
+        <v>96584</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R87" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,45 +9706,55 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125721877</v>
+        <v>125722060</v>
       </c>
       <c r="B88" t="n">
-        <v>75005</v>
+        <v>57811</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397502</v>
+        <v>397606</v>
       </c>
       <c r="R88" t="n">
-        <v>6697866</v>
+        <v>6697859</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,32 +9813,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B89" t="n">
-        <v>96584</v>
+        <v>75005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9838,10 +9848,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R89" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9900,55 +9910,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125722060</v>
+        <v>125721877</v>
       </c>
       <c r="B90" t="n">
-        <v>57811</v>
+        <v>75005</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397606</v>
+        <v>397502</v>
       </c>
       <c r="R90" t="n">
-        <v>6697859</v>
+        <v>6697866</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720024</v>
+        <v>125720994</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397180</v>
+        <v>397124</v>
       </c>
       <c r="R99" t="n">
-        <v>6697817</v>
+        <v>6697850</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,19 +10894,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>18:07</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10917,26 +10912,46 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125720994</v>
+        <v>125721374</v>
       </c>
       <c r="B100" t="n">
-        <v>80070</v>
+        <v>79585</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10944,21 +10959,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10968,10 +10983,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397124</v>
+        <v>397266</v>
       </c>
       <c r="R100" t="n">
-        <v>6697850</v>
+        <v>6697866</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11006,11 +11021,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11019,26 +11029,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11055,10 +11045,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125721374</v>
+        <v>125720024</v>
       </c>
       <c r="B101" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11066,21 +11056,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11090,13 +11080,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397266</v>
+        <v>397180</v>
       </c>
       <c r="R101" t="n">
-        <v>6697866</v>
+        <v>6697817</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11123,9 +11113,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -6668,45 +6668,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125699868</v>
+        <v>125698310</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>43933</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398211</v>
+        <v>398204</v>
       </c>
       <c r="R58" t="n">
-        <v>6697955</v>
+        <v>6697895</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,45 +6770,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125698905</v>
+        <v>125696921</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398367</v>
+        <v>397904</v>
       </c>
       <c r="R59" t="n">
-        <v>6697942</v>
+        <v>6697885</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6959,50 +6973,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125698310</v>
+        <v>125699868</v>
       </c>
       <c r="B61" t="n">
-        <v>43933</v>
+        <v>78967</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398204</v>
+        <v>398211</v>
       </c>
       <c r="R61" t="n">
-        <v>6697895</v>
+        <v>6697955</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7061,54 +7070,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125696921</v>
+        <v>125698905</v>
       </c>
       <c r="B62" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>397904</v>
+        <v>398367</v>
       </c>
       <c r="R62" t="n">
-        <v>6697885</v>
+        <v>6697942</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9609,32 +9609,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B87" t="n">
-        <v>96584</v>
+        <v>75005</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R87" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,55 +9706,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125722060</v>
+        <v>125721877</v>
       </c>
       <c r="B88" t="n">
-        <v>57811</v>
+        <v>75005</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397606</v>
+        <v>397502</v>
       </c>
       <c r="R88" t="n">
-        <v>6697859</v>
+        <v>6697866</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9813,32 +9803,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B89" t="n">
-        <v>75005</v>
+        <v>96584</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9848,10 +9838,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R89" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9910,45 +9900,55 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125721877</v>
+        <v>125722060</v>
       </c>
       <c r="B90" t="n">
-        <v>75005</v>
+        <v>57811</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397502</v>
+        <v>397606</v>
       </c>
       <c r="R90" t="n">
-        <v>6697866</v>
+        <v>6697859</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2957,7 +2957,7 @@
         <v>125425784</v>
       </c>
       <c r="B22" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>125420220</v>
       </c>
       <c r="B23" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>125418813</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>125419081</v>
       </c>
       <c r="B25" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>125423621</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>125422828</v>
       </c>
       <c r="B27" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>125419993</v>
       </c>
       <c r="B28" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125426865</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,38 +3837,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B30" t="n">
-        <v>98248</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3876,13 +3880,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R30" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,7 +3934,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3949,42 +3952,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419158</v>
+        <v>125419083</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>98251</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3992,13 +3991,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397890</v>
+        <v>397869</v>
       </c>
       <c r="R31" t="n">
-        <v>6697937</v>
+        <v>6697920</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4027,7 +4026,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4037,7 +4036,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,6 +4045,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>125419996</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>125447089</v>
       </c>
       <c r="B33" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>125447044</v>
       </c>
       <c r="B34" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>125698845</v>
       </c>
       <c r="B35" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>125700228</v>
       </c>
       <c r="B36" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125700601</v>
+        <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>96584</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,34 +4802,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397968</v>
+        <v>398216</v>
       </c>
       <c r="R39" t="n">
-        <v>6697927</v>
+        <v>6697912</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4990,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125698253</v>
+        <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>96587</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5001,34 +5001,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398216</v>
+        <v>397968</v>
       </c>
       <c r="R41" t="n">
-        <v>6697912</v>
+        <v>6697927</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5090,7 +5090,7 @@
         <v>125700252</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>125696883</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>125699772</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>125700268</v>
       </c>
       <c r="B45" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125698599</v>
+        <v>125700296</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5506,14 +5506,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398320</v>
+        <v>397992</v>
       </c>
       <c r="R46" t="n">
-        <v>6697905</v>
+        <v>6697940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
         <v>125697091</v>
       </c>
       <c r="B47" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125698761</v>
+        <v>125698599</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398357</v>
+        <v>398320</v>
       </c>
       <c r="R48" t="n">
-        <v>6697925</v>
+        <v>6697905</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125700296</v>
+        <v>125698761</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5797,14 +5797,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397992</v>
+        <v>398357</v>
       </c>
       <c r="R49" t="n">
-        <v>6697940</v>
+        <v>6697925</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
         <v>125699923</v>
       </c>
       <c r="B50" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>125700564</v>
       </c>
       <c r="B51" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>125699719</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>125697120</v>
       </c>
       <c r="B53" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>75006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R54" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>75005</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R55" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
         <v>125697625</v>
       </c>
       <c r="B56" t="n">
-        <v>80942</v>
+        <v>80943</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>125696949</v>
       </c>
       <c r="B57" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,50 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125698310</v>
+        <v>125699868</v>
       </c>
       <c r="B58" t="n">
-        <v>43933</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398204</v>
+        <v>398211</v>
       </c>
       <c r="R58" t="n">
-        <v>6697895</v>
+        <v>6697955</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6770,54 +6765,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125696921</v>
+        <v>125698905</v>
       </c>
       <c r="B59" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>397904</v>
+        <v>398367</v>
       </c>
       <c r="R59" t="n">
-        <v>6697885</v>
+        <v>6697942</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6876,10 +6862,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125700680</v>
+        <v>125698310</v>
       </c>
       <c r="B60" t="n">
-        <v>75005</v>
+        <v>43933</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6887,34 +6873,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>397883</v>
+        <v>398204</v>
       </c>
       <c r="R60" t="n">
-        <v>6697899</v>
+        <v>6697895</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6973,45 +6964,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125699868</v>
+        <v>125700680</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>75006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398211</v>
+        <v>397883</v>
       </c>
       <c r="R61" t="n">
-        <v>6697955</v>
+        <v>6697899</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,45 +7061,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125698905</v>
+        <v>125696921</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398367</v>
+        <v>397904</v>
       </c>
       <c r="R62" t="n">
-        <v>6697942</v>
+        <v>6697885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>125697394</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>125700176</v>
       </c>
       <c r="B66" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>125698508</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>125698527</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>125719981</v>
       </c>
       <c r="B69" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>125721577</v>
       </c>
       <c r="B70" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>125721868</v>
       </c>
       <c r="B71" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8074,32 +8074,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>75006</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R72" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B73" t="n">
-        <v>75005</v>
+        <v>78968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R73" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125720225</v>
+        <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>397113</v>
+        <v>397145</v>
       </c>
       <c r="R74" t="n">
-        <v>6697838</v>
+        <v>6697801</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8349,6 +8349,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8365,10 +8385,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125719936</v>
+        <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8400,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397145</v>
+        <v>397113</v>
       </c>
       <c r="R75" t="n">
-        <v>6697801</v>
+        <v>6697838</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8446,26 +8466,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721492</v>
+        <v>125721012</v>
       </c>
       <c r="B76" t="n">
-        <v>78999</v>
+        <v>80031</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397334</v>
+        <v>397124</v>
       </c>
       <c r="R76" t="n">
-        <v>6697894</v>
+        <v>6697850</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,26 +8563,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8602,7 +8582,7 @@
         <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8696,32 +8676,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721012</v>
+        <v>125721492</v>
       </c>
       <c r="B78" t="n">
-        <v>80030</v>
+        <v>79000</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8731,10 +8711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397124</v>
+        <v>397334</v>
       </c>
       <c r="R78" t="n">
-        <v>6697850</v>
+        <v>6697894</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8777,6 +8757,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8796,7 +8796,7 @@
         <v>125720843</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125722033</v>
       </c>
       <c r="B80" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>125722105</v>
       </c>
       <c r="B81" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721536</v>
+        <v>125720079</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>80031</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397361</v>
+        <v>397116</v>
       </c>
       <c r="R82" t="n">
-        <v>6697854</v>
+        <v>6697830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,6 +9185,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9201,32 +9221,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B83" t="n">
-        <v>80030</v>
+        <v>78727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9236,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R83" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9282,26 +9302,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B84" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R84" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B85" t="n">
-        <v>80942</v>
+        <v>78968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9426,34 +9426,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R85" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>80943</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9523,34 +9523,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R86" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9609,32 +9609,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B87" t="n">
-        <v>75005</v>
+        <v>96587</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R87" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,10 +9706,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125721877</v>
+        <v>125720473</v>
       </c>
       <c r="B88" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9737,14 +9737,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397502</v>
+        <v>397024</v>
       </c>
       <c r="R88" t="n">
-        <v>6697866</v>
+        <v>6697840</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,45 +9803,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720934</v>
+        <v>125721877</v>
       </c>
       <c r="B89" t="n">
-        <v>96584</v>
+        <v>75006</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397112</v>
+        <v>397502</v>
       </c>
       <c r="R89" t="n">
-        <v>6697860</v>
+        <v>6697866</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10010,7 +10010,7 @@
         <v>125721765</v>
       </c>
       <c r="B91" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>125721651</v>
       </c>
       <c r="B94" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>125721224</v>
       </c>
       <c r="B95" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>125721700</v>
       </c>
       <c r="B96" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10598,45 +10598,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125720121</v>
+        <v>125720782</v>
       </c>
       <c r="B97" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>397116</v>
+        <v>397014</v>
       </c>
       <c r="R97" t="n">
-        <v>6697806</v>
+        <v>6697845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10671,11 +10680,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10684,26 +10688,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10720,54 +10704,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125720782</v>
+        <v>125720121</v>
       </c>
       <c r="B98" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>397014</v>
+        <v>397116</v>
       </c>
       <c r="R98" t="n">
-        <v>6697845</v>
+        <v>6697806</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10802,6 +10777,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10810,6 +10790,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -10829,7 +10829,7 @@
         <v>125720994</v>
       </c>
       <c r="B99" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>125721374</v>
       </c>
       <c r="B100" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>125720024</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -3837,42 +3837,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419158</v>
+        <v>125419083</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>98251</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3880,13 +3876,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397890</v>
+        <v>397869</v>
       </c>
       <c r="R30" t="n">
-        <v>6697937</v>
+        <v>6697920</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3915,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,6 +3930,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3952,38 +3949,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B31" t="n">
-        <v>98251</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3991,13 +3992,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R31" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4026,7 +4027,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4036,7 +4037,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,7 +4046,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B35" t="n">
         <v>75006</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R35" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B36" t="n">
         <v>75006</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R36" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -6668,45 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125699868</v>
+        <v>125700680</v>
       </c>
       <c r="B58" t="n">
-        <v>78968</v>
+        <v>75006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398211</v>
+        <v>397883</v>
       </c>
       <c r="R58" t="n">
-        <v>6697955</v>
+        <v>6697899</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125698905</v>
+        <v>125699868</v>
       </c>
       <c r="B59" t="n">
         <v>78968</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398367</v>
+        <v>398211</v>
       </c>
       <c r="R59" t="n">
-        <v>6697942</v>
+        <v>6697955</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6862,50 +6862,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125698310</v>
+        <v>125698905</v>
       </c>
       <c r="B60" t="n">
-        <v>43933</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398204</v>
+        <v>398367</v>
       </c>
       <c r="R60" t="n">
-        <v>6697895</v>
+        <v>6697942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,10 +6959,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125700680</v>
+        <v>125698310</v>
       </c>
       <c r="B61" t="n">
-        <v>75006</v>
+        <v>43933</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6975,34 +6970,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>397883</v>
+        <v>398204</v>
       </c>
       <c r="R61" t="n">
-        <v>6697899</v>
+        <v>6697895</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721012</v>
+        <v>125721492</v>
       </c>
       <c r="B76" t="n">
-        <v>80031</v>
+        <v>79000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397124</v>
+        <v>397334</v>
       </c>
       <c r="R76" t="n">
-        <v>6697850</v>
+        <v>6697894</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,6 +8563,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8579,32 +8599,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125720252</v>
+        <v>125721012</v>
       </c>
       <c r="B77" t="n">
-        <v>98334</v>
+        <v>80031</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8614,10 +8634,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397108</v>
+        <v>397124</v>
       </c>
       <c r="R77" t="n">
-        <v>6697837</v>
+        <v>6697850</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8676,32 +8696,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B78" t="n">
-        <v>79000</v>
+        <v>98334</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8711,10 +8731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R78" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8757,26 +8777,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10598,54 +10598,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125720782</v>
+        <v>125720121</v>
       </c>
       <c r="B97" t="n">
-        <v>98334</v>
+        <v>80071</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>397014</v>
+        <v>397116</v>
       </c>
       <c r="R97" t="n">
-        <v>6697845</v>
+        <v>6697806</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10680,6 +10671,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10688,6 +10684,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10704,45 +10720,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125720121</v>
+        <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>397116</v>
+        <v>397014</v>
       </c>
       <c r="R98" t="n">
-        <v>6697806</v>
+        <v>6697845</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10777,11 +10802,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10790,26 +10810,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -2957,7 +2957,7 @@
         <v>125425784</v>
       </c>
       <c r="B22" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>125420220</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>125418813</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>125423621</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125426865</v>
       </c>
       <c r="B29" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125419083</v>
       </c>
       <c r="B30" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>125419996</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>125700252</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>125696883</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>75006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R44" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B45" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R45" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>125700296</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5572,45 +5572,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125697091</v>
+        <v>125698599</v>
       </c>
       <c r="B47" t="n">
-        <v>79054</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397938</v>
+        <v>398320</v>
       </c>
       <c r="R47" t="n">
-        <v>6697903</v>
+        <v>6697905</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,45 +5669,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125698599</v>
+        <v>125697091</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>79058</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398320</v>
+        <v>397938</v>
       </c>
       <c r="R48" t="n">
-        <v>6697905</v>
+        <v>6697903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5769,7 +5769,7 @@
         <v>125698761</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5863,54 +5863,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125699923</v>
+        <v>125700564</v>
       </c>
       <c r="B50" t="n">
-        <v>98334</v>
+        <v>79058</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398147</v>
+        <v>397969</v>
       </c>
       <c r="R50" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,6 +5944,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5969,45 +5980,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125700564</v>
+        <v>125699923</v>
       </c>
       <c r="B51" t="n">
-        <v>79054</v>
+        <v>98338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>397969</v>
+        <v>398147</v>
       </c>
       <c r="R51" t="n">
-        <v>6697932</v>
+        <v>6697955</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,26 +6070,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6089,7 +6089,7 @@
         <v>125699719</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>125697625</v>
       </c>
       <c r="B56" t="n">
-        <v>80943</v>
+        <v>80947</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>125696949</v>
       </c>
       <c r="B57" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,45 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125700680</v>
+        <v>125698905</v>
       </c>
       <c r="B58" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>397883</v>
+        <v>398367</v>
       </c>
       <c r="R58" t="n">
-        <v>6697899</v>
+        <v>6697942</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,45 +6765,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125699868</v>
+        <v>125698310</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>43933</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398211</v>
+        <v>398204</v>
       </c>
       <c r="R59" t="n">
-        <v>6697955</v>
+        <v>6697895</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6862,45 +6867,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125698905</v>
+        <v>125696921</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398367</v>
+        <v>397904</v>
       </c>
       <c r="R60" t="n">
-        <v>6697942</v>
+        <v>6697885</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6959,50 +6973,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125698310</v>
+        <v>125699868</v>
       </c>
       <c r="B61" t="n">
-        <v>43933</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398204</v>
+        <v>398211</v>
       </c>
       <c r="R61" t="n">
-        <v>6697895</v>
+        <v>6697955</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7061,54 +7070,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125696921</v>
+        <v>125700680</v>
       </c>
       <c r="B62" t="n">
-        <v>98334</v>
+        <v>75006</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>397904</v>
+        <v>397883</v>
       </c>
       <c r="R62" t="n">
-        <v>6697885</v>
+        <v>6697899</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>125697394</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>125698508</v>
       </c>
       <c r="B67" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>125698527</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>125721577</v>
       </c>
       <c r="B70" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>125721868</v>
       </c>
       <c r="B71" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>125721710</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721492</v>
+        <v>125721012</v>
       </c>
       <c r="B76" t="n">
-        <v>79000</v>
+        <v>80035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397334</v>
+        <v>397124</v>
       </c>
       <c r="R76" t="n">
-        <v>6697894</v>
+        <v>6697850</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,26 +8563,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8599,32 +8579,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721012</v>
+        <v>125721492</v>
       </c>
       <c r="B77" t="n">
-        <v>80031</v>
+        <v>79004</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8634,10 +8614,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397124</v>
+        <v>397334</v>
       </c>
       <c r="R77" t="n">
-        <v>6697850</v>
+        <v>6697894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8680,6 +8660,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8699,7 +8699,7 @@
         <v>125720252</v>
       </c>
       <c r="B78" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>125720843</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125722033</v>
       </c>
       <c r="B80" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>125722105</v>
       </c>
       <c r="B81" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720079</v>
+        <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>80031</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397116</v>
+        <v>397361</v>
       </c>
       <c r="R82" t="n">
-        <v>6697830</v>
+        <v>6697854</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,26 +9185,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9221,32 +9201,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>78727</v>
+        <v>80035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R83" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,6 +9282,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R84" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9418,7 +9418,7 @@
         <v>125722112</v>
       </c>
       <c r="B85" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>125721835</v>
       </c>
       <c r="B86" t="n">
-        <v>80943</v>
+        <v>80947</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720934</v>
+        <v>125722060</v>
       </c>
       <c r="B87" t="n">
-        <v>96587</v>
+        <v>57811</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9620,34 +9620,44 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397112</v>
+        <v>397606</v>
       </c>
       <c r="R87" t="n">
-        <v>6697860</v>
+        <v>6697859</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9900,10 +9910,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125722060</v>
+        <v>125720934</v>
       </c>
       <c r="B90" t="n">
-        <v>57811</v>
+        <v>96591</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9911,44 +9921,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397606</v>
+        <v>397112</v>
       </c>
       <c r="R90" t="n">
-        <v>6697859</v>
+        <v>6697860</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10010,7 +10010,7 @@
         <v>125721765</v>
       </c>
       <c r="B91" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125721651</v>
+        <v>125721224</v>
       </c>
       <c r="B94" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397346</v>
+        <v>397232</v>
       </c>
       <c r="R94" t="n">
-        <v>6697842</v>
+        <v>6697857</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125721224</v>
+        <v>125721651</v>
       </c>
       <c r="B95" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397232</v>
+        <v>397346</v>
       </c>
       <c r="R95" t="n">
-        <v>6697857</v>
+        <v>6697842</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10504,7 +10504,7 @@
         <v>125721700</v>
       </c>
       <c r="B96" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>125720121</v>
       </c>
       <c r="B97" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720994</v>
+        <v>125720024</v>
       </c>
       <c r="B99" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397124</v>
+        <v>397180</v>
       </c>
       <c r="R99" t="n">
-        <v>6697850</v>
+        <v>6697817</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,14 +10894,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10912,46 +10917,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721374</v>
+        <v>125720994</v>
       </c>
       <c r="B100" t="n">
-        <v>79586</v>
+        <v>80075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10959,21 +10944,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10983,10 +10968,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397266</v>
+        <v>397124</v>
       </c>
       <c r="R100" t="n">
-        <v>6697866</v>
+        <v>6697850</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11021,6 +11006,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11029,6 +11019,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11045,10 +11055,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125720024</v>
+        <v>125721374</v>
       </c>
       <c r="B101" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11056,21 +11066,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11080,13 +11090,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397180</v>
+        <v>397266</v>
       </c>
       <c r="R101" t="n">
-        <v>6697817</v>
+        <v>6697866</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11113,19 +11123,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -3837,38 +3837,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B30" t="n">
-        <v>98255</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3876,13 +3880,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R30" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,7 +3934,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3949,42 +3952,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419158</v>
+        <v>125419083</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>98255</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3992,13 +3991,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397890</v>
+        <v>397869</v>
       </c>
       <c r="R31" t="n">
-        <v>6697937</v>
+        <v>6697920</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4027,7 +4026,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4037,7 +4036,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,6 +4045,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B54" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R54" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>75006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R55" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -8074,32 +8074,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B72" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R72" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>75006</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R73" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721012</v>
+        <v>125720252</v>
       </c>
       <c r="B76" t="n">
-        <v>80035</v>
+        <v>98338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397124</v>
+        <v>397108</v>
       </c>
       <c r="R76" t="n">
-        <v>6697850</v>
+        <v>6697837</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8579,32 +8579,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721492</v>
+        <v>125721012</v>
       </c>
       <c r="B77" t="n">
-        <v>79004</v>
+        <v>80035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397334</v>
+        <v>397124</v>
       </c>
       <c r="R77" t="n">
-        <v>6697894</v>
+        <v>6697850</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8660,26 +8660,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8696,32 +8676,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B78" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8731,10 +8711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R78" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8777,6 +8757,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721536</v>
+        <v>125720079</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>80035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397361</v>
+        <v>397116</v>
       </c>
       <c r="R82" t="n">
-        <v>6697854</v>
+        <v>6697830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,6 +9185,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9201,32 +9221,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B83" t="n">
-        <v>80035</v>
+        <v>78731</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9236,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R83" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9282,26 +9302,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B84" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R84" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9716,32 +9716,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B88" t="n">
-        <v>75006</v>
+        <v>96591</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R88" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125721877</v>
+        <v>125720473</v>
       </c>
       <c r="B89" t="n">
         <v>75006</v>
@@ -9844,14 +9844,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397502</v>
+        <v>397024</v>
       </c>
       <c r="R89" t="n">
-        <v>6697866</v>
+        <v>6697840</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9910,45 +9910,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125720934</v>
+        <v>125721877</v>
       </c>
       <c r="B90" t="n">
-        <v>96591</v>
+        <v>75006</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397112</v>
+        <v>397502</v>
       </c>
       <c r="R90" t="n">
-        <v>6697860</v>
+        <v>6697866</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125721224</v>
+        <v>125721651</v>
       </c>
       <c r="B94" t="n">
         <v>78972</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397232</v>
+        <v>397346</v>
       </c>
       <c r="R94" t="n">
-        <v>6697857</v>
+        <v>6697842</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125721651</v>
+        <v>125721224</v>
       </c>
       <c r="B95" t="n">
         <v>78972</v>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397346</v>
+        <v>397232</v>
       </c>
       <c r="R95" t="n">
-        <v>6697842</v>
+        <v>6697857</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -3719,7 +3719,7 @@
         <v>125426865</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,42 +3837,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419158</v>
+        <v>125419083</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>98256</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3880,13 +3876,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397890</v>
+        <v>397869</v>
       </c>
       <c r="R30" t="n">
-        <v>6697937</v>
+        <v>6697920</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3915,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,6 +3930,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3952,38 +3949,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B31" t="n">
-        <v>98255</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3991,13 +3992,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R31" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4026,7 +4027,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4036,7 +4037,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,7 +4046,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B35" t="n">
         <v>75006</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R35" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B36" t="n">
         <v>75006</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R36" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,45 +4791,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698253</v>
+        <v>125698359</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>43933</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398216</v>
+        <v>398223</v>
       </c>
       <c r="R39" t="n">
-        <v>6697912</v>
+        <v>6697923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4888,50 +4893,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B40" t="n">
-        <v>43933</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R40" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
         <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B44" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R44" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>75006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R45" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125700296</v>
+        <v>125698599</v>
       </c>
       <c r="B46" t="n">
         <v>78972</v>
@@ -5506,14 +5506,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>397992</v>
+        <v>398320</v>
       </c>
       <c r="R46" t="n">
-        <v>6697940</v>
+        <v>6697905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125698599</v>
+        <v>125698761</v>
       </c>
       <c r="B47" t="n">
         <v>78972</v>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398320</v>
+        <v>398357</v>
       </c>
       <c r="R47" t="n">
-        <v>6697905</v>
+        <v>6697925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5766,7 +5766,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125698761</v>
+        <v>125700296</v>
       </c>
       <c r="B49" t="n">
         <v>78972</v>
@@ -5797,14 +5797,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>398357</v>
+        <v>397992</v>
       </c>
       <c r="R49" t="n">
-        <v>6697925</v>
+        <v>6697940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5863,45 +5863,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125700564</v>
+        <v>125699923</v>
       </c>
       <c r="B50" t="n">
-        <v>79058</v>
+        <v>98339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>397969</v>
+        <v>398147</v>
       </c>
       <c r="R50" t="n">
-        <v>6697932</v>
+        <v>6697955</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,26 +5953,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5980,54 +5969,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125699923</v>
+        <v>125700564</v>
       </c>
       <c r="B51" t="n">
-        <v>98338</v>
+        <v>79058</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398147</v>
+        <v>397969</v>
       </c>
       <c r="R51" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6070,6 +6050,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>75006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R54" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R55" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6668,45 +6668,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125698905</v>
+        <v>125696921</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398367</v>
+        <v>397904</v>
       </c>
       <c r="R58" t="n">
-        <v>6697942</v>
+        <v>6697885</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,10 +6774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125698310</v>
+        <v>125700680</v>
       </c>
       <c r="B59" t="n">
-        <v>43933</v>
+        <v>75006</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6776,39 +6785,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398204</v>
+        <v>397883</v>
       </c>
       <c r="R59" t="n">
-        <v>6697895</v>
+        <v>6697899</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6867,54 +6871,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125696921</v>
+        <v>125699868</v>
       </c>
       <c r="B60" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>397904</v>
+        <v>398211</v>
       </c>
       <c r="R60" t="n">
-        <v>6697885</v>
+        <v>6697955</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6973,7 +6968,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125699868</v>
+        <v>125698905</v>
       </c>
       <c r="B61" t="n">
         <v>78972</v>
@@ -7008,10 +7003,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398211</v>
+        <v>398367</v>
       </c>
       <c r="R61" t="n">
-        <v>6697955</v>
+        <v>6697942</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,10 +7065,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125700680</v>
+        <v>125698310</v>
       </c>
       <c r="B62" t="n">
-        <v>75006</v>
+        <v>43933</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7081,34 +7076,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>397883</v>
+        <v>398204</v>
       </c>
       <c r="R62" t="n">
-        <v>6697899</v>
+        <v>6697895</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B70" t="n">
-        <v>80075</v>
+        <v>91232</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7871,34 +7871,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R70" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,26 +7941,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7977,10 +7957,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B71" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7988,34 +7968,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R71" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8058,6 +8038,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8271,7 +8271,7 @@
         <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B76" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R76" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,6 +8563,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8579,32 +8599,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721012</v>
+        <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>80035</v>
+        <v>98339</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8614,10 +8634,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397124</v>
+        <v>397108</v>
       </c>
       <c r="R77" t="n">
-        <v>6697850</v>
+        <v>6697837</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8676,32 +8696,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721492</v>
+        <v>125721012</v>
       </c>
       <c r="B78" t="n">
-        <v>79004</v>
+        <v>80035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8711,10 +8731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397334</v>
+        <v>397124</v>
       </c>
       <c r="R78" t="n">
-        <v>6697894</v>
+        <v>6697850</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8757,26 +8777,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720079</v>
+        <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>80035</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397116</v>
+        <v>397361</v>
       </c>
       <c r="R82" t="n">
-        <v>6697830</v>
+        <v>6697854</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,26 +9185,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9221,32 +9201,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>78731</v>
+        <v>80035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R83" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,6 +9282,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R84" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>80947</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9426,34 +9426,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R85" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B86" t="n">
-        <v>80947</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9523,34 +9523,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R86" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9719,7 +9719,7 @@
         <v>125720934</v>
       </c>
       <c r="B88" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125721651</v>
+        <v>125721224</v>
       </c>
       <c r="B94" t="n">
         <v>78972</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397346</v>
+        <v>397232</v>
       </c>
       <c r="R94" t="n">
-        <v>6697842</v>
+        <v>6697857</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125721224</v>
+        <v>125721651</v>
       </c>
       <c r="B95" t="n">
         <v>78972</v>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397232</v>
+        <v>397346</v>
       </c>
       <c r="R95" t="n">
-        <v>6697857</v>
+        <v>6697842</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720024</v>
+        <v>125720994</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397180</v>
+        <v>397124</v>
       </c>
       <c r="R99" t="n">
-        <v>6697817</v>
+        <v>6697850</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,19 +10894,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>18:07</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10917,26 +10912,46 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125720994</v>
+        <v>125721374</v>
       </c>
       <c r="B100" t="n">
-        <v>80075</v>
+        <v>79590</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10944,21 +10959,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10968,10 +10983,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397124</v>
+        <v>397266</v>
       </c>
       <c r="R100" t="n">
-        <v>6697850</v>
+        <v>6697866</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11006,11 +11021,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11019,26 +11029,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11055,10 +11045,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125721374</v>
+        <v>125720024</v>
       </c>
       <c r="B101" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11066,21 +11056,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11090,13 +11080,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397266</v>
+        <v>397180</v>
       </c>
       <c r="R101" t="n">
-        <v>6697866</v>
+        <v>6697817</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11123,9 +11113,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4791,50 +4791,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>43933</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R39" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,45 +4888,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698253</v>
+        <v>125698359</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>43933</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398216</v>
+        <v>398223</v>
       </c>
       <c r="R40" t="n">
-        <v>6697912</v>
+        <v>6697923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721536</v>
+        <v>125720079</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>80035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397361</v>
+        <v>397116</v>
       </c>
       <c r="R82" t="n">
-        <v>6697854</v>
+        <v>6697830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,6 +9185,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9201,32 +9221,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B83" t="n">
-        <v>80035</v>
+        <v>78731</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9236,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R83" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9282,26 +9302,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B84" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R84" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4791,45 +4791,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698253</v>
+        <v>125698359</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>43933</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398216</v>
+        <v>398223</v>
       </c>
       <c r="R39" t="n">
-        <v>6697912</v>
+        <v>6697923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4888,50 +4893,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B40" t="n">
-        <v>43933</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R40" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720079</v>
+        <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>80035</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397116</v>
+        <v>397361</v>
       </c>
       <c r="R82" t="n">
-        <v>6697830</v>
+        <v>6697854</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,26 +9185,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9221,32 +9201,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>78731</v>
+        <v>80035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R83" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,6 +9282,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R84" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>125422828</v>
       </c>
       <c r="B27" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>125419993</v>
       </c>
       <c r="B28" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125426865</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,38 +3837,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125419083</v>
+        <v>125419158</v>
       </c>
       <c r="B30" t="n">
-        <v>98256</v>
+        <v>57652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3876,13 +3880,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397869</v>
+        <v>397890</v>
       </c>
       <c r="R30" t="n">
-        <v>6697920</v>
+        <v>6697937</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,7 +3934,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3949,42 +3952,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125419158</v>
+        <v>125419083</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>98258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3992,13 +3991,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397890</v>
+        <v>397869</v>
       </c>
       <c r="R31" t="n">
-        <v>6697937</v>
+        <v>6697920</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4027,7 +4026,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4037,7 +4036,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,6 +4045,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>125419996</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>125447089</v>
       </c>
       <c r="B33" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>125447044</v>
       </c>
       <c r="B34" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>125698845</v>
       </c>
       <c r="B35" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>125700228</v>
       </c>
       <c r="B36" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>125698646</v>
       </c>
       <c r="B37" t="n">
-        <v>43933</v>
+        <v>43934</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>125698575</v>
       </c>
       <c r="B38" t="n">
-        <v>43933</v>
+        <v>43934</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>125698359</v>
       </c>
       <c r="B39" t="n">
-        <v>43933</v>
+        <v>43934</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>125698253</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>125700252</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>125696883</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>75007</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R44" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B45" t="n">
-        <v>75006</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R45" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>125698599</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5572,45 +5572,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125698761</v>
+        <v>125697091</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>79059</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>398357</v>
+        <v>397938</v>
       </c>
       <c r="R47" t="n">
-        <v>6697925</v>
+        <v>6697903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,45 +5669,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125697091</v>
+        <v>125698761</v>
       </c>
       <c r="B48" t="n">
-        <v>79058</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397938</v>
+        <v>398357</v>
       </c>
       <c r="R48" t="n">
-        <v>6697903</v>
+        <v>6697925</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5769,7 +5769,7 @@
         <v>125700296</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>125699923</v>
       </c>
       <c r="B50" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>125700564</v>
       </c>
       <c r="B51" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>125699719</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>125697120</v>
       </c>
       <c r="B53" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>125697246</v>
       </c>
       <c r="B54" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>125697625</v>
       </c>
       <c r="B56" t="n">
-        <v>80947</v>
+        <v>80948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>125696949</v>
       </c>
       <c r="B57" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,54 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125696921</v>
+        <v>125699868</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>397904</v>
+        <v>398211</v>
       </c>
       <c r="R58" t="n">
-        <v>6697885</v>
+        <v>6697955</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6774,45 +6765,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125700680</v>
+        <v>125698905</v>
       </c>
       <c r="B59" t="n">
-        <v>75006</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>397883</v>
+        <v>398367</v>
       </c>
       <c r="R59" t="n">
-        <v>6697899</v>
+        <v>6697942</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,45 +6862,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125699868</v>
+        <v>125700680</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>75007</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398211</v>
+        <v>397883</v>
       </c>
       <c r="R60" t="n">
-        <v>6697955</v>
+        <v>6697899</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6968,45 +6959,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125698905</v>
+        <v>125698310</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>43934</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398367</v>
+        <v>398204</v>
       </c>
       <c r="R61" t="n">
-        <v>6697942</v>
+        <v>6697895</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7065,50 +7061,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125698310</v>
+        <v>125696921</v>
       </c>
       <c r="B62" t="n">
-        <v>43933</v>
+        <v>98341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398204</v>
+        <v>397904</v>
       </c>
       <c r="R62" t="n">
-        <v>6697895</v>
+        <v>6697885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7170,7 @@
         <v>125698710</v>
       </c>
       <c r="B63" t="n">
-        <v>43933</v>
+        <v>43934</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>125697394</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>125700176</v>
       </c>
       <c r="B66" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>125698508</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>125698527</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>125719981</v>
       </c>
       <c r="B69" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B70" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7871,34 +7871,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R70" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,6 +7941,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7957,10 +7977,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>91234</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,34 +7988,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R71" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8038,26 +8058,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8074,32 +8074,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B72" t="n">
-        <v>78972</v>
+        <v>75007</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R72" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B73" t="n">
-        <v>75006</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R73" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8271,7 +8271,7 @@
         <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B76" t="n">
-        <v>79004</v>
+        <v>98341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R76" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,26 +8563,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8599,32 +8579,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B77" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8634,10 +8614,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R77" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8680,6 +8660,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8699,7 +8699,7 @@
         <v>125721012</v>
       </c>
       <c r="B78" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>125720843</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>125722033</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>125722105</v>
       </c>
       <c r="B81" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>125721835</v>
       </c>
       <c r="B85" t="n">
-        <v>80947</v>
+        <v>80948</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>125722112</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125722060</v>
+        <v>125720934</v>
       </c>
       <c r="B87" t="n">
-        <v>57811</v>
+        <v>96594</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9620,44 +9620,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397606</v>
+        <v>397112</v>
       </c>
       <c r="R87" t="n">
-        <v>6697859</v>
+        <v>6697860</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9716,32 +9706,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B88" t="n">
-        <v>96592</v>
+        <v>75007</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9751,10 +9741,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R88" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9813,10 +9803,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720473</v>
+        <v>125721877</v>
       </c>
       <c r="B89" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9844,14 +9834,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397024</v>
+        <v>397502</v>
       </c>
       <c r="R89" t="n">
-        <v>6697840</v>
+        <v>6697866</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9910,45 +9900,55 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125721877</v>
+        <v>125722060</v>
       </c>
       <c r="B90" t="n">
-        <v>75006</v>
+        <v>57812</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397502</v>
+        <v>397606</v>
       </c>
       <c r="R90" t="n">
-        <v>6697866</v>
+        <v>6697859</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10010,7 +10010,7 @@
         <v>125721765</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125721224</v>
+        <v>125721651</v>
       </c>
       <c r="B94" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397232</v>
+        <v>397346</v>
       </c>
       <c r="R94" t="n">
-        <v>6697857</v>
+        <v>6697842</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125721651</v>
+        <v>125721224</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397346</v>
+        <v>397232</v>
       </c>
       <c r="R95" t="n">
-        <v>6697842</v>
+        <v>6697857</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10504,7 +10504,7 @@
         <v>125721700</v>
       </c>
       <c r="B96" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>125720121</v>
       </c>
       <c r="B97" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720994</v>
+        <v>125720024</v>
       </c>
       <c r="B99" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397124</v>
+        <v>397180</v>
       </c>
       <c r="R99" t="n">
-        <v>6697850</v>
+        <v>6697817</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,14 +10894,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10912,46 +10917,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721374</v>
+        <v>125720994</v>
       </c>
       <c r="B100" t="n">
-        <v>79590</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10959,21 +10944,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10983,10 +10968,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397266</v>
+        <v>397124</v>
       </c>
       <c r="R100" t="n">
-        <v>6697866</v>
+        <v>6697850</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11021,6 +11006,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11029,6 +11019,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11045,10 +11055,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125720024</v>
+        <v>125721374</v>
       </c>
       <c r="B101" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11056,21 +11066,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11080,13 +11090,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397180</v>
+        <v>397266</v>
       </c>
       <c r="R101" t="n">
-        <v>6697817</v>
+        <v>6697866</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11113,19 +11123,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B54" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R54" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R55" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B76" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R76" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,6 +8563,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8579,32 +8599,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>79005</v>
+        <v>98341</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8614,10 +8634,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R77" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8660,26 +8680,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721536</v>
+        <v>125720079</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>80036</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397361</v>
+        <v>397116</v>
       </c>
       <c r="R82" t="n">
-        <v>6697854</v>
+        <v>6697830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,6 +9185,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9201,32 +9221,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B83" t="n">
-        <v>80036</v>
+        <v>78732</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9236,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R83" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9282,26 +9302,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B84" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R84" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B35" t="n">
         <v>75007</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R35" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B36" t="n">
         <v>75007</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R36" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,50 +4791,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>43934</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R39" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,45 +4888,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698253</v>
+        <v>125698359</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>43934</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398216</v>
+        <v>398223</v>
       </c>
       <c r="R40" t="n">
-        <v>6697912</v>
+        <v>6697923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
         <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B44" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R44" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R45" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
         <v>125699923</v>
       </c>
       <c r="B50" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6668,45 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125699868</v>
+        <v>125700680</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398211</v>
+        <v>397883</v>
       </c>
       <c r="R58" t="n">
-        <v>6697955</v>
+        <v>6697899</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125698905</v>
+        <v>125699868</v>
       </c>
       <c r="B59" t="n">
         <v>78973</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398367</v>
+        <v>398211</v>
       </c>
       <c r="R59" t="n">
-        <v>6697942</v>
+        <v>6697955</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6862,45 +6862,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125700680</v>
+        <v>125698905</v>
       </c>
       <c r="B60" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>397883</v>
+        <v>398367</v>
       </c>
       <c r="R60" t="n">
-        <v>6697899</v>
+        <v>6697942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7064,7 +7064,7 @@
         <v>125696921</v>
       </c>
       <c r="B62" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>91236</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7871,34 +7871,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R70" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,26 +7941,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7977,10 +7957,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B71" t="n">
-        <v>91234</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7988,34 +7968,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R71" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8058,6 +8038,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8074,32 +8074,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B72" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R72" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R73" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125719936</v>
+        <v>125720225</v>
       </c>
       <c r="B74" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>397145</v>
+        <v>397113</v>
       </c>
       <c r="R74" t="n">
-        <v>6697801</v>
+        <v>6697838</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8349,26 +8349,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8385,10 +8365,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125720225</v>
+        <v>125719936</v>
       </c>
       <c r="B75" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8420,10 +8400,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397113</v>
+        <v>397145</v>
       </c>
       <c r="R75" t="n">
-        <v>6697838</v>
+        <v>6697801</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8466,6 +8446,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B76" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R76" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,26 +8563,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8599,32 +8579,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125720252</v>
+        <v>125721012</v>
       </c>
       <c r="B77" t="n">
-        <v>98341</v>
+        <v>80036</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8634,10 +8614,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397108</v>
+        <v>397124</v>
       </c>
       <c r="R77" t="n">
-        <v>6697837</v>
+        <v>6697850</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8696,32 +8676,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721012</v>
+        <v>125721492</v>
       </c>
       <c r="B78" t="n">
-        <v>80036</v>
+        <v>79005</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8731,10 +8711,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397124</v>
+        <v>397334</v>
       </c>
       <c r="R78" t="n">
-        <v>6697850</v>
+        <v>6697894</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8777,6 +8757,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720079</v>
+        <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>80036</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397116</v>
+        <v>397361</v>
       </c>
       <c r="R82" t="n">
-        <v>6697830</v>
+        <v>6697854</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,26 +9185,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9221,32 +9201,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>78732</v>
+        <v>80036</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R83" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,6 +9282,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R84" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B85" t="n">
-        <v>80948</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9426,34 +9426,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R85" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>80948</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9523,34 +9523,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R86" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9609,32 +9609,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B87" t="n">
-        <v>96594</v>
+        <v>75007</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R87" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,7 +9706,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125720473</v>
+        <v>125721877</v>
       </c>
       <c r="B88" t="n">
         <v>75007</v>
@@ -9737,14 +9737,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397024</v>
+        <v>397502</v>
       </c>
       <c r="R88" t="n">
-        <v>6697840</v>
+        <v>6697866</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,45 +9803,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125721877</v>
+        <v>125720934</v>
       </c>
       <c r="B89" t="n">
-        <v>75007</v>
+        <v>96596</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397502</v>
+        <v>397112</v>
       </c>
       <c r="R89" t="n">
-        <v>6697866</v>
+        <v>6697860</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720024</v>
+        <v>125720994</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397180</v>
+        <v>397124</v>
       </c>
       <c r="R99" t="n">
-        <v>6697817</v>
+        <v>6697850</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,19 +10894,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>18:07</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10917,26 +10912,46 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125720994</v>
+        <v>125721374</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>79591</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10944,21 +10959,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10968,10 +10983,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397124</v>
+        <v>397266</v>
       </c>
       <c r="R100" t="n">
-        <v>6697850</v>
+        <v>6697866</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11006,11 +11021,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11019,26 +11029,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11055,10 +11045,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125721374</v>
+        <v>125720024</v>
       </c>
       <c r="B101" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11066,21 +11056,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11090,13 +11080,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397266</v>
+        <v>397180</v>
       </c>
       <c r="R101" t="n">
-        <v>6697866</v>
+        <v>6697817</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11123,9 +11113,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B35" t="n">
         <v>75007</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R35" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B36" t="n">
         <v>75007</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R36" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -6668,45 +6668,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125700680</v>
+        <v>125699868</v>
       </c>
       <c r="B58" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>397883</v>
+        <v>398211</v>
       </c>
       <c r="R58" t="n">
-        <v>6697899</v>
+        <v>6697955</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125699868</v>
+        <v>125698905</v>
       </c>
       <c r="B59" t="n">
         <v>78973</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398211</v>
+        <v>398367</v>
       </c>
       <c r="R59" t="n">
-        <v>6697955</v>
+        <v>6697942</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6862,45 +6862,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125698905</v>
+        <v>125698310</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>43934</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398367</v>
+        <v>398204</v>
       </c>
       <c r="R60" t="n">
-        <v>6697942</v>
+        <v>6697895</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6959,10 +6964,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125698310</v>
+        <v>125700680</v>
       </c>
       <c r="B61" t="n">
-        <v>43934</v>
+        <v>75007</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6970,39 +6975,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398204</v>
+        <v>397883</v>
       </c>
       <c r="R61" t="n">
-        <v>6697895</v>
+        <v>6697899</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8482,32 +8482,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B76" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R76" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8563,6 +8563,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8676,32 +8696,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B78" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8711,10 +8731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R78" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8757,26 +8777,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B35" t="n">
         <v>75007</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R35" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B36" t="n">
         <v>75007</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R36" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,45 +4791,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698253</v>
+        <v>125698359</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>43934</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398216</v>
+        <v>398223</v>
       </c>
       <c r="R39" t="n">
-        <v>6697912</v>
+        <v>6697923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4888,50 +4893,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B40" t="n">
-        <v>43934</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R40" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
         <v>125700601</v>
       </c>
       <c r="B41" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5863,54 +5863,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125699923</v>
+        <v>125700564</v>
       </c>
       <c r="B50" t="n">
-        <v>98343</v>
+        <v>79059</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398147</v>
+        <v>397969</v>
       </c>
       <c r="R50" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,6 +5944,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5969,45 +5980,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125700564</v>
+        <v>125699923</v>
       </c>
       <c r="B51" t="n">
-        <v>79059</v>
+        <v>98345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>397969</v>
+        <v>398147</v>
       </c>
       <c r="R51" t="n">
-        <v>6697932</v>
+        <v>6697955</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,26 +6070,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R54" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R55" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6668,45 +6668,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125699868</v>
+        <v>125696921</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398211</v>
+        <v>397904</v>
       </c>
       <c r="R58" t="n">
-        <v>6697955</v>
+        <v>6697885</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,45 +6774,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125698905</v>
+        <v>125700680</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>398367</v>
+        <v>397883</v>
       </c>
       <c r="R59" t="n">
-        <v>6697942</v>
+        <v>6697899</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6964,45 +6973,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125700680</v>
+        <v>125699868</v>
       </c>
       <c r="B61" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>397883</v>
+        <v>398211</v>
       </c>
       <c r="R61" t="n">
-        <v>6697899</v>
+        <v>6697955</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7061,54 +7070,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125696921</v>
+        <v>125698905</v>
       </c>
       <c r="B62" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>397904</v>
+        <v>398367</v>
       </c>
       <c r="R62" t="n">
-        <v>6697885</v>
+        <v>6697942</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125698508</v>
+        <v>125698527</v>
       </c>
       <c r="B67" t="n">
         <v>78973</v>
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398307</v>
+        <v>398294</v>
       </c>
       <c r="R67" t="n">
-        <v>6697923</v>
+        <v>6697907</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125698527</v>
+        <v>125698508</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398294</v>
+        <v>398307</v>
       </c>
       <c r="R68" t="n">
-        <v>6697907</v>
+        <v>6697923</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7863,7 +7863,7 @@
         <v>125721868</v>
       </c>
       <c r="B70" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8074,32 +8074,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R72" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B73" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R73" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8268,10 +8268,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125720225</v>
+        <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>397113</v>
+        <v>397145</v>
       </c>
       <c r="R74" t="n">
-        <v>6697838</v>
+        <v>6697801</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8349,6 +8349,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8365,10 +8385,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125719936</v>
+        <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8400,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397145</v>
+        <v>397113</v>
       </c>
       <c r="R75" t="n">
-        <v>6697801</v>
+        <v>6697838</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8446,26 +8466,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8599,32 +8599,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721012</v>
+        <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>80036</v>
+        <v>98345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397124</v>
+        <v>397108</v>
       </c>
       <c r="R77" t="n">
-        <v>6697850</v>
+        <v>6697837</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8696,32 +8696,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125720252</v>
+        <v>125721012</v>
       </c>
       <c r="B78" t="n">
-        <v>98343</v>
+        <v>80036</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397108</v>
+        <v>397124</v>
       </c>
       <c r="R78" t="n">
-        <v>6697837</v>
+        <v>6697850</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125720843</v>
+        <v>125722033</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8824,14 +8824,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>397075</v>
+        <v>397606</v>
       </c>
       <c r="R79" t="n">
-        <v>6697869</v>
+        <v>6697859</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8890,7 +8890,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125722033</v>
+        <v>125720843</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8921,14 +8921,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>397606</v>
+        <v>397075</v>
       </c>
       <c r="R80" t="n">
-        <v>6697859</v>
+        <v>6697869</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>80948</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9426,34 +9426,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R85" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B86" t="n">
-        <v>80948</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9523,34 +9523,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R86" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720473</v>
+        <v>125721877</v>
       </c>
       <c r="B87" t="n">
         <v>75007</v>
@@ -9640,14 +9640,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397024</v>
+        <v>397502</v>
       </c>
       <c r="R87" t="n">
-        <v>6697840</v>
+        <v>6697866</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,45 +9706,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125721877</v>
+        <v>125720934</v>
       </c>
       <c r="B88" t="n">
-        <v>75007</v>
+        <v>96598</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397502</v>
+        <v>397112</v>
       </c>
       <c r="R88" t="n">
-        <v>6697866</v>
+        <v>6697860</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,32 +9803,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B89" t="n">
-        <v>96596</v>
+        <v>75007</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9838,10 +9838,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R89" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720994</v>
+        <v>125720024</v>
       </c>
       <c r="B99" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397124</v>
+        <v>397180</v>
       </c>
       <c r="R99" t="n">
-        <v>6697850</v>
+        <v>6697817</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,14 +10894,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10912,46 +10917,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721374</v>
+        <v>125720994</v>
       </c>
       <c r="B100" t="n">
-        <v>79591</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10959,21 +10944,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10983,10 +10968,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397266</v>
+        <v>397124</v>
       </c>
       <c r="R100" t="n">
-        <v>6697866</v>
+        <v>6697850</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11021,6 +11006,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11029,6 +11019,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11045,10 +11055,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125720024</v>
+        <v>125721374</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11056,21 +11066,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11080,13 +11090,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397180</v>
+        <v>397266</v>
       </c>
       <c r="R101" t="n">
-        <v>6697817</v>
+        <v>6697866</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11113,19 +11123,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B35" t="n">
         <v>75007</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R35" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B36" t="n">
         <v>75007</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R36" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,50 +4791,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>43934</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R39" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4893,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698253</v>
+        <v>125700601</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>96598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4904,34 +4899,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398216</v>
+        <v>397968</v>
       </c>
       <c r="R40" t="n">
-        <v>6697912</v>
+        <v>6697927</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4990,45 +4985,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125700601</v>
+        <v>125698359</v>
       </c>
       <c r="B41" t="n">
-        <v>96598</v>
+        <v>43934</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397968</v>
+        <v>398223</v>
       </c>
       <c r="R41" t="n">
-        <v>6697927</v>
+        <v>6697923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6668,54 +6668,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125696921</v>
+        <v>125698310</v>
       </c>
       <c r="B58" t="n">
-        <v>98345</v>
+        <v>43934</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>397904</v>
+        <v>398204</v>
       </c>
       <c r="R58" t="n">
-        <v>6697885</v>
+        <v>6697895</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6774,45 +6770,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125700680</v>
+        <v>125699868</v>
       </c>
       <c r="B59" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>397883</v>
+        <v>398211</v>
       </c>
       <c r="R59" t="n">
-        <v>6697899</v>
+        <v>6697955</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,50 +6867,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125698310</v>
+        <v>125698905</v>
       </c>
       <c r="B60" t="n">
-        <v>43934</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>398204</v>
+        <v>398367</v>
       </c>
       <c r="R60" t="n">
-        <v>6697895</v>
+        <v>6697942</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6973,45 +6964,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125699868</v>
+        <v>125696921</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>398211</v>
+        <v>397904</v>
       </c>
       <c r="R61" t="n">
-        <v>6697955</v>
+        <v>6697885</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,45 +7070,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125698905</v>
+        <v>125700680</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>398367</v>
+        <v>397883</v>
       </c>
       <c r="R62" t="n">
-        <v>6697942</v>
+        <v>6697899</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -10598,45 +10598,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125720121</v>
+        <v>125720782</v>
       </c>
       <c r="B97" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>397116</v>
+        <v>397014</v>
       </c>
       <c r="R97" t="n">
-        <v>6697806</v>
+        <v>6697845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10671,11 +10680,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10684,26 +10688,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10720,54 +10704,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125720782</v>
+        <v>125720121</v>
       </c>
       <c r="B98" t="n">
-        <v>98345</v>
+        <v>80076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>397014</v>
+        <v>397116</v>
       </c>
       <c r="R98" t="n">
-        <v>6697845</v>
+        <v>6697806</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10802,6 +10777,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10810,6 +10790,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,10 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B35" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R35" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B36" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R36" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4794,7 +4794,7 @@
         <v>125698253</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>125700601</v>
       </c>
       <c r="B40" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>125700252</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>125696883</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>75011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R44" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B45" t="n">
-        <v>75007</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R45" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
         <v>125698599</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>125697091</v>
       </c>
       <c r="B47" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>125698761</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>125700296</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>125700564</v>
       </c>
       <c r="B50" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>125699923</v>
       </c>
       <c r="B51" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>125699719</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>125697120</v>
       </c>
       <c r="B53" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B54" t="n">
-        <v>75007</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R54" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>75011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R55" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
         <v>125697625</v>
       </c>
       <c r="B56" t="n">
-        <v>80948</v>
+        <v>80952</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>125696949</v>
       </c>
       <c r="B57" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6668,10 +6668,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125698310</v>
+        <v>125700680</v>
       </c>
       <c r="B58" t="n">
-        <v>43934</v>
+        <v>75011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6679,39 +6679,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>398204</v>
+        <v>397883</v>
       </c>
       <c r="R58" t="n">
-        <v>6697895</v>
+        <v>6697899</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6773,7 +6768,7 @@
         <v>125699868</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6870,7 +6865,7 @@
         <v>125698905</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6964,54 +6959,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125696921</v>
+        <v>125698310</v>
       </c>
       <c r="B61" t="n">
-        <v>98345</v>
+        <v>43934</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>397904</v>
+        <v>398204</v>
       </c>
       <c r="R61" t="n">
-        <v>6697885</v>
+        <v>6697895</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,45 +7061,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125700680</v>
+        <v>125696921</v>
       </c>
       <c r="B62" t="n">
-        <v>75007</v>
+        <v>98349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>397883</v>
+        <v>397904</v>
       </c>
       <c r="R62" t="n">
-        <v>6697899</v>
+        <v>6697885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7375,45 +7375,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125697394</v>
+        <v>125700176</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>75011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>397995</v>
+        <v>398044</v>
       </c>
       <c r="R65" t="n">
-        <v>6697902</v>
+        <v>6697944</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7472,45 +7472,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125700176</v>
+        <v>125697394</v>
       </c>
       <c r="B66" t="n">
-        <v>75007</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>398044</v>
+        <v>397995</v>
       </c>
       <c r="R66" t="n">
-        <v>6697944</v>
+        <v>6697902</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125698527</v>
+        <v>125698508</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>398294</v>
+        <v>398307</v>
       </c>
       <c r="R67" t="n">
-        <v>6697907</v>
+        <v>6697923</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7666,10 +7666,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125698508</v>
+        <v>125698527</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>398307</v>
+        <v>398294</v>
       </c>
       <c r="R68" t="n">
-        <v>6697923</v>
+        <v>6697907</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7766,7 +7766,7 @@
         <v>125719981</v>
       </c>
       <c r="B69" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>125721868</v>
       </c>
       <c r="B70" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>125721577</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8074,32 +8074,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B72" t="n">
-        <v>75007</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R72" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8171,32 +8171,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>75011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R73" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8271,7 +8271,7 @@
         <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>125721492</v>
       </c>
       <c r="B76" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>125721012</v>
       </c>
       <c r="B78" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8793,10 +8793,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125722033</v>
+        <v>125720843</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8824,14 +8824,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>397606</v>
+        <v>397075</v>
       </c>
       <c r="R79" t="n">
-        <v>6697859</v>
+        <v>6697869</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125720843</v>
+        <v>125722033</v>
       </c>
       <c r="B80" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8921,14 +8921,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>397075</v>
+        <v>397606</v>
       </c>
       <c r="R80" t="n">
-        <v>6697869</v>
+        <v>6697859</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
         <v>125722105</v>
       </c>
       <c r="B81" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B85" t="n">
-        <v>80948</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9426,34 +9426,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R85" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>80952</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9523,34 +9523,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R86" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9609,45 +9609,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125721877</v>
+        <v>125720934</v>
       </c>
       <c r="B87" t="n">
-        <v>75007</v>
+        <v>96602</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397502</v>
+        <v>397112</v>
       </c>
       <c r="R87" t="n">
-        <v>6697866</v>
+        <v>6697860</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9706,32 +9706,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B88" t="n">
-        <v>96598</v>
+        <v>75011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R88" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,10 +9803,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125720473</v>
+        <v>125721877</v>
       </c>
       <c r="B89" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9834,14 +9834,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397024</v>
+        <v>397502</v>
       </c>
       <c r="R89" t="n">
-        <v>6697840</v>
+        <v>6697866</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9903,7 +9903,7 @@
         <v>125722060</v>
       </c>
       <c r="B90" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>125721765</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>125720604</v>
       </c>
       <c r="B93" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>125721651</v>
       </c>
       <c r="B94" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>125721224</v>
       </c>
       <c r="B95" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>125721700</v>
       </c>
       <c r="B96" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10598,54 +10598,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125720782</v>
+        <v>125720121</v>
       </c>
       <c r="B97" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>397014</v>
+        <v>397116</v>
       </c>
       <c r="R97" t="n">
-        <v>6697845</v>
+        <v>6697806</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10680,6 +10671,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10688,6 +10684,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10704,45 +10720,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125720121</v>
+        <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>397116</v>
+        <v>397014</v>
       </c>
       <c r="R98" t="n">
-        <v>6697806</v>
+        <v>6697845</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10777,11 +10802,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10790,26 +10810,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -10829,7 +10829,7 @@
         <v>125720024</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>125720994</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>125721374</v>
       </c>
       <c r="B101" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B35" t="n">
         <v>75011</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R35" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B36" t="n">
         <v>75011</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R36" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125698253</v>
+        <v>125700601</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>96602</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,34 +4802,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>398216</v>
+        <v>397968</v>
       </c>
       <c r="R39" t="n">
-        <v>6697912</v>
+        <v>6697927</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4888,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125700601</v>
+        <v>125698253</v>
       </c>
       <c r="B40" t="n">
-        <v>96602</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,34 +4899,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397968</v>
+        <v>398216</v>
       </c>
       <c r="R40" t="n">
-        <v>6697927</v>
+        <v>6697912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5281,45 +5281,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125700268</v>
+        <v>125699772</v>
       </c>
       <c r="B44" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>398012</v>
+        <v>398238</v>
       </c>
       <c r="R44" t="n">
-        <v>6697933</v>
+        <v>6697953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,45 +5378,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125699772</v>
+        <v>125700268</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>75011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>398238</v>
+        <v>398012</v>
       </c>
       <c r="R45" t="n">
-        <v>6697953</v>
+        <v>6697933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5863,45 +5863,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125700564</v>
+        <v>125699923</v>
       </c>
       <c r="B50" t="n">
-        <v>79063</v>
+        <v>98349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>397969</v>
+        <v>398147</v>
       </c>
       <c r="R50" t="n">
-        <v>6697932</v>
+        <v>6697955</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,26 +5953,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5980,54 +5969,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125699923</v>
+        <v>125700564</v>
       </c>
       <c r="B51" t="n">
-        <v>98349</v>
+        <v>79063</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>398147</v>
+        <v>397969</v>
       </c>
       <c r="R51" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6070,6 +6050,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721536</v>
+        <v>125720079</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>80040</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397361</v>
+        <v>397116</v>
       </c>
       <c r="R82" t="n">
-        <v>6697854</v>
+        <v>6697830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,6 +9185,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9201,32 +9221,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B83" t="n">
-        <v>80040</v>
+        <v>78736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9236,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R83" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9282,26 +9302,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B84" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R84" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>80952</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9426,34 +9426,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R85" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B86" t="n">
-        <v>80952</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9523,34 +9523,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R86" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -4393,7 +4393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125698845</v>
+        <v>125700228</v>
       </c>
       <c r="B35" t="n">
         <v>75011</v>
@@ -4424,14 +4424,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>398355</v>
+        <v>398025</v>
       </c>
       <c r="R35" t="n">
-        <v>6697919</v>
+        <v>6697933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125700228</v>
+        <v>125698845</v>
       </c>
       <c r="B36" t="n">
         <v>75011</v>
@@ -4521,14 +4521,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>398025</v>
+        <v>398355</v>
       </c>
       <c r="R36" t="n">
-        <v>6697933</v>
+        <v>6697919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4794,7 +4794,7 @@
         <v>125700601</v>
       </c>
       <c r="B39" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,45 +4888,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125698253</v>
+        <v>125698359</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>43934</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>398216</v>
+        <v>398223</v>
       </c>
       <c r="R40" t="n">
-        <v>6697912</v>
+        <v>6697923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4985,50 +4990,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125698359</v>
+        <v>125698253</v>
       </c>
       <c r="B41" t="n">
-        <v>43934</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>398223</v>
+        <v>398216</v>
       </c>
       <c r="R41" t="n">
-        <v>6697923</v>
+        <v>6697912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125698599</v>
+        <v>125700296</v>
       </c>
       <c r="B46" t="n">
         <v>78977</v>
@@ -5506,14 +5506,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>398320</v>
+        <v>397992</v>
       </c>
       <c r="R46" t="n">
-        <v>6697905</v>
+        <v>6697940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5572,45 +5572,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125697091</v>
+        <v>125698599</v>
       </c>
       <c r="B47" t="n">
-        <v>79063</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397938</v>
+        <v>398320</v>
       </c>
       <c r="R47" t="n">
-        <v>6697903</v>
+        <v>6697905</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,45 +5669,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125698761</v>
+        <v>125697091</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>79063</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>398357</v>
+        <v>397938</v>
       </c>
       <c r="R48" t="n">
-        <v>6697925</v>
+        <v>6697903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5766,7 +5766,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125700296</v>
+        <v>125698761</v>
       </c>
       <c r="B49" t="n">
         <v>78977</v>
@@ -5797,14 +5797,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397992</v>
+        <v>398357</v>
       </c>
       <c r="R49" t="n">
-        <v>6697940</v>
+        <v>6697925</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5863,54 +5863,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125699923</v>
+        <v>125700564</v>
       </c>
       <c r="B50" t="n">
-        <v>98349</v>
+        <v>79063</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>398147</v>
+        <v>397969</v>
       </c>
       <c r="R50" t="n">
-        <v>6697955</v>
+        <v>6697932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,6 +5944,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5969,45 +5980,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125700564</v>
+        <v>125699923</v>
       </c>
       <c r="B51" t="n">
-        <v>79063</v>
+        <v>98352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>397969</v>
+        <v>398147</v>
       </c>
       <c r="R51" t="n">
-        <v>6697932</v>
+        <v>6697955</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,26 +6070,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6280,32 +6280,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125700356</v>
+        <v>125697246</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>75011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>397983</v>
+        <v>397988</v>
       </c>
       <c r="R54" t="n">
-        <v>6697932</v>
+        <v>6697895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,32 +6377,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125697246</v>
+        <v>125700356</v>
       </c>
       <c r="B55" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>397988</v>
+        <v>397983</v>
       </c>
       <c r="R55" t="n">
-        <v>6697895</v>
+        <v>6697932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7064,7 +7064,7 @@
         <v>125696921</v>
       </c>
       <c r="B62" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>125697063</v>
       </c>
       <c r="B64" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7375,45 +7375,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125700176</v>
+        <v>125697394</v>
       </c>
       <c r="B65" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>398044</v>
+        <v>397995</v>
       </c>
       <c r="R65" t="n">
-        <v>6697944</v>
+        <v>6697902</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7472,45 +7472,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125697394</v>
+        <v>125700176</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>75011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>397995</v>
+        <v>398044</v>
       </c>
       <c r="R66" t="n">
-        <v>6697902</v>
+        <v>6697944</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B70" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7871,34 +7871,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R70" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,6 +7941,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7957,10 +7977,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B71" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,34 +7988,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R71" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8038,26 +8058,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8271,7 +8271,7 @@
         <v>125719936</v>
       </c>
       <c r="B74" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>125720225</v>
       </c>
       <c r="B75" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>125720252</v>
       </c>
       <c r="B77" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720079</v>
+        <v>125721536</v>
       </c>
       <c r="B82" t="n">
-        <v>80040</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397116</v>
+        <v>397361</v>
       </c>
       <c r="R82" t="n">
-        <v>6697830</v>
+        <v>6697854</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,26 +9185,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9221,32 +9201,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B83" t="n">
-        <v>78736</v>
+        <v>80040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9256,10 +9236,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R83" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9302,6 +9282,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R84" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9612,7 +9612,7 @@
         <v>125720934</v>
       </c>
       <c r="B87" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>125720910</v>
       </c>
       <c r="B92" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>125720782</v>
       </c>
       <c r="B98" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720024</v>
+        <v>125720994</v>
       </c>
       <c r="B99" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397180</v>
+        <v>397124</v>
       </c>
       <c r="R99" t="n">
-        <v>6697817</v>
+        <v>6697850</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10894,19 +10894,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>18:07</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10917,26 +10912,46 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125720994</v>
+        <v>125721374</v>
       </c>
       <c r="B100" t="n">
-        <v>80080</v>
+        <v>79595</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10944,21 +10959,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10968,10 +10983,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397124</v>
+        <v>397266</v>
       </c>
       <c r="R100" t="n">
-        <v>6697850</v>
+        <v>6697866</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11006,11 +11021,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11019,26 +11029,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11055,10 +11045,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125721374</v>
+        <v>125720024</v>
       </c>
       <c r="B101" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11066,21 +11056,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11090,13 +11080,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397266</v>
+        <v>397180</v>
       </c>
       <c r="R101" t="n">
-        <v>6697866</v>
+        <v>6697817</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11123,9 +11113,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11140,12 +11140,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -7860,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B70" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7871,34 +7871,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R70" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7941,26 +7941,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7977,10 +7957,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B71" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7988,34 +7968,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R71" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8058,6 +8038,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9104,32 +9104,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721536</v>
+        <v>125720079</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>80040</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397361</v>
+        <v>397116</v>
       </c>
       <c r="R82" t="n">
-        <v>6697854</v>
+        <v>6697830</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,6 +9185,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9201,32 +9221,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B83" t="n">
-        <v>80040</v>
+        <v>78736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9236,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R83" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9282,26 +9302,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B84" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9329,21 +9329,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R84" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11150,6 +11150,113 @@
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126608319</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>397411</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6697838</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Maja Larsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Maja Larsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -7766,7 +7766,7 @@
         <v>125419408</v>
       </c>
       <c r="B69" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>125419873</v>
       </c>
       <c r="B70" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>125419887</v>
       </c>
       <c r="B71" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>125419637</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>126608319</v>
       </c>
       <c r="B106" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -7766,7 +7766,7 @@
         <v>125419408</v>
       </c>
       <c r="B69" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>125419873</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>125419887</v>
       </c>
       <c r="B71" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>125419637</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>126608319</v>
       </c>
       <c r="B106" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -7766,7 +7766,7 @@
         <v>125419408</v>
       </c>
       <c r="B69" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>125419873</v>
       </c>
       <c r="B70" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>125419887</v>
       </c>
       <c r="B71" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>125419637</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8200,48 +8200,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125719981</v>
+        <v>130013052</v>
       </c>
       <c r="B73" t="n">
-        <v>75011</v>
+        <v>80192</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397142</v>
+        <v>398130</v>
       </c>
       <c r="R73" t="n">
-        <v>6697816</v>
+        <v>6697932</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8285,57 +8285,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125721868</v>
+        <v>125719981</v>
       </c>
       <c r="B74" t="n">
-        <v>91242</v>
+        <v>75011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>397473</v>
+        <v>397142</v>
       </c>
       <c r="R74" t="n">
-        <v>6697852</v>
+        <v>6697816</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B75" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8405,34 +8405,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R75" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8475,26 +8475,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8511,10 +8491,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721710</v>
+        <v>125721577</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8522,21 +8502,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8546,10 +8526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397381</v>
+        <v>397395</v>
       </c>
       <c r="R76" t="n">
-        <v>6697850</v>
+        <v>6697867</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8592,6 +8572,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8608,32 +8608,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B77" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R77" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8705,32 +8705,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125719936</v>
+        <v>125721040</v>
       </c>
       <c r="B78" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397145</v>
+        <v>397171</v>
       </c>
       <c r="R78" t="n">
-        <v>6697801</v>
+        <v>6697871</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8786,26 +8786,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8822,7 +8802,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125720225</v>
+        <v>125719936</v>
       </c>
       <c r="B79" t="n">
         <v>96605</v>
@@ -8857,10 +8837,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>397113</v>
+        <v>397145</v>
       </c>
       <c r="R79" t="n">
-        <v>6697838</v>
+        <v>6697801</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8903,6 +8883,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8919,10 +8919,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125721492</v>
+        <v>125720225</v>
       </c>
       <c r="B80" t="n">
-        <v>79009</v>
+        <v>96605</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>397334</v>
+        <v>397113</v>
       </c>
       <c r="R80" t="n">
-        <v>6697894</v>
+        <v>6697838</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9000,26 +9000,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9036,32 +9016,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B81" t="n">
-        <v>98352</v>
+        <v>79009</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9071,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R81" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9117,6 +9097,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9133,32 +9133,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721012</v>
+        <v>125720252</v>
       </c>
       <c r="B82" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9168,10 +9168,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397124</v>
+        <v>397108</v>
       </c>
       <c r="R82" t="n">
-        <v>6697850</v>
+        <v>6697837</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9230,32 +9230,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720843</v>
+        <v>125721012</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>80040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397075</v>
+        <v>397124</v>
       </c>
       <c r="R83" t="n">
-        <v>6697869</v>
+        <v>6697850</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125722033</v>
+        <v>125720843</v>
       </c>
       <c r="B84" t="n">
         <v>78977</v>
@@ -9358,14 +9358,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397606</v>
+        <v>397075</v>
       </c>
       <c r="R84" t="n">
-        <v>6697859</v>
+        <v>6697869</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9424,10 +9424,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125722105</v>
+        <v>125722033</v>
       </c>
       <c r="B85" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9435,21 +9435,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397625</v>
+        <v>397606</v>
       </c>
       <c r="R85" t="n">
-        <v>6697852</v>
+        <v>6697859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9505,26 +9505,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9541,45 +9521,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125720079</v>
+        <v>125722105</v>
       </c>
       <c r="B86" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397116</v>
+        <v>397625</v>
       </c>
       <c r="R86" t="n">
-        <v>6697830</v>
+        <v>6697852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9625,22 +9605,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Betula pendula</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9658,32 +9638,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B87" t="n">
-        <v>78736</v>
+        <v>80040</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9693,10 +9673,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R87" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9739,6 +9719,26 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -9755,10 +9755,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9766,21 +9766,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R88" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9852,10 +9852,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125721835</v>
+        <v>125721536</v>
       </c>
       <c r="B89" t="n">
-        <v>80952</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9863,34 +9863,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397433</v>
+        <v>397361</v>
       </c>
       <c r="R89" t="n">
-        <v>6697891</v>
+        <v>6697854</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9949,10 +9949,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>80952</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9960,34 +9960,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R90" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10046,10 +10046,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125720934</v>
+        <v>125722112</v>
       </c>
       <c r="B91" t="n">
-        <v>96605</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10057,34 +10057,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>397112</v>
+        <v>397625</v>
       </c>
       <c r="R91" t="n">
-        <v>6697860</v>
+        <v>6697852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10143,32 +10143,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B92" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R92" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125721877</v>
+        <v>125720473</v>
       </c>
       <c r="B93" t="n">
         <v>75011</v>
@@ -10271,14 +10271,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>397502</v>
+        <v>397024</v>
       </c>
       <c r="R93" t="n">
-        <v>6697866</v>
+        <v>6697840</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10337,55 +10337,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125722060</v>
+        <v>125721877</v>
       </c>
       <c r="B94" t="n">
-        <v>57816</v>
+        <v>75011</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397606</v>
+        <v>397502</v>
       </c>
       <c r="R94" t="n">
-        <v>6697859</v>
+        <v>6697866</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10444,10 +10434,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125721765</v>
+        <v>125722060</v>
       </c>
       <c r="B95" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10455,34 +10445,44 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397383</v>
+        <v>397606</v>
       </c>
       <c r="R95" t="n">
-        <v>6697865</v>
+        <v>6697859</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10541,54 +10541,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125720910</v>
+        <v>125721765</v>
       </c>
       <c r="B96" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>397092</v>
+        <v>397383</v>
       </c>
       <c r="R96" t="n">
-        <v>6697872</v>
+        <v>6697865</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10647,45 +10638,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125720604</v>
+        <v>125720910</v>
       </c>
       <c r="B97" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>396991</v>
+        <v>397092</v>
       </c>
       <c r="R97" t="n">
-        <v>6697837</v>
+        <v>6697872</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10744,10 +10744,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125721651</v>
+        <v>125720604</v>
       </c>
       <c r="B98" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10755,21 +10755,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>397346</v>
+        <v>396991</v>
       </c>
       <c r="R98" t="n">
-        <v>6697842</v>
+        <v>6697837</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10841,7 +10841,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125721224</v>
+        <v>125721651</v>
       </c>
       <c r="B99" t="n">
         <v>78977</v>
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397232</v>
+        <v>397346</v>
       </c>
       <c r="R99" t="n">
-        <v>6697857</v>
+        <v>6697842</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721700</v>
+        <v>125721224</v>
       </c>
       <c r="B100" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10949,21 +10949,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397397</v>
+        <v>397232</v>
       </c>
       <c r="R100" t="n">
-        <v>6697850</v>
+        <v>6697857</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11035,10 +11035,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125720121</v>
+        <v>125721700</v>
       </c>
       <c r="B101" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11046,21 +11046,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397116</v>
+        <v>397397</v>
       </c>
       <c r="R101" t="n">
-        <v>6697806</v>
+        <v>6697850</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11108,11 +11108,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11121,26 +11116,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11157,54 +11132,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125720782</v>
+        <v>125720121</v>
       </c>
       <c r="B102" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>397014</v>
+        <v>397116</v>
       </c>
       <c r="R102" t="n">
-        <v>6697845</v>
+        <v>6697806</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11239,6 +11205,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11247,6 +11218,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11263,45 +11254,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125720994</v>
+        <v>125720782</v>
       </c>
       <c r="B103" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>397124</v>
+        <v>397014</v>
       </c>
       <c r="R103" t="n">
-        <v>6697850</v>
+        <v>6697845</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11336,11 +11336,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11349,26 +11344,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11385,10 +11360,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125721374</v>
+        <v>125720994</v>
       </c>
       <c r="B104" t="n">
-        <v>79595</v>
+        <v>80080</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11396,21 +11371,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11420,10 +11395,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>397266</v>
+        <v>397124</v>
       </c>
       <c r="R104" t="n">
-        <v>6697866</v>
+        <v>6697850</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11458,6 +11433,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11466,6 +11446,26 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11482,10 +11482,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125720024</v>
+        <v>125721374</v>
       </c>
       <c r="B105" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11493,21 +11493,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11517,13 +11517,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>397180</v>
+        <v>397266</v>
       </c>
       <c r="R105" t="n">
-        <v>6697817</v>
+        <v>6697866</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11550,19 +11550,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>18:07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11577,22 +11567,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126608319</v>
+        <v>125720024</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>78977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11620,17 +11610,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>397411</v>
+        <v>397180</v>
       </c>
       <c r="R106" t="n">
-        <v>6697838</v>
+        <v>6697817</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11654,22 +11644,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11684,15 +11674,122 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126608319</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>397411</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6697838</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
           <t>Maja Larsson</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
+      <c r="AX107" t="inlineStr">
         <is>
           <t>Maja Larsson</t>
         </is>
       </c>
-      <c r="AY106" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -8203,7 +8203,7 @@
         <v>130013052</v>
       </c>
       <c r="B73" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -8203,7 +8203,7 @@
         <v>130013052</v>
       </c>
       <c r="B73" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8200,48 +8200,62 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130013052</v>
+        <v>129922856</v>
       </c>
       <c r="B73" t="n">
-        <v>80200</v>
+        <v>98833</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>398130</v>
+        <v>397909</v>
       </c>
       <c r="R73" t="n">
-        <v>6697932</v>
+        <v>6697934</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8263,14 +8277,19 @@
           <t>Norra Ny</t>
         </is>
       </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>S-Tor-0391</t>
+        </is>
+      </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8285,60 +8304,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125719981</v>
+        <v>130013052</v>
       </c>
       <c r="B74" t="n">
-        <v>75011</v>
+        <v>80200</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>397142</v>
+        <v>398130</v>
       </c>
       <c r="R74" t="n">
-        <v>6697816</v>
+        <v>6697932</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8362,12 +8385,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8382,57 +8405,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125721868</v>
+        <v>125719981</v>
       </c>
       <c r="B75" t="n">
-        <v>91242</v>
+        <v>75011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397473</v>
+        <v>397142</v>
       </c>
       <c r="R75" t="n">
-        <v>6697852</v>
+        <v>6697816</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,10 +8514,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721577</v>
+        <v>125721868</v>
       </c>
       <c r="B76" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8502,34 +8525,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397395</v>
+        <v>397473</v>
       </c>
       <c r="R76" t="n">
-        <v>6697867</v>
+        <v>6697852</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8572,26 +8595,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8608,10 +8611,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721710</v>
+        <v>125721577</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8619,21 +8622,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8643,10 +8646,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397381</v>
+        <v>397395</v>
       </c>
       <c r="R77" t="n">
-        <v>6697850</v>
+        <v>6697867</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8689,6 +8692,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8705,32 +8728,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721040</v>
+        <v>125721710</v>
       </c>
       <c r="B78" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8740,10 +8763,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397171</v>
+        <v>397381</v>
       </c>
       <c r="R78" t="n">
-        <v>6697871</v>
+        <v>6697850</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8802,32 +8825,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125719936</v>
+        <v>125721040</v>
       </c>
       <c r="B79" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8837,10 +8860,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>397145</v>
+        <v>397171</v>
       </c>
       <c r="R79" t="n">
-        <v>6697801</v>
+        <v>6697871</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8883,26 +8906,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8919,7 +8922,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125720225</v>
+        <v>125719936</v>
       </c>
       <c r="B80" t="n">
         <v>96605</v>
@@ -8954,10 +8957,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>397113</v>
+        <v>397145</v>
       </c>
       <c r="R80" t="n">
-        <v>6697838</v>
+        <v>6697801</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9000,6 +9003,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9016,10 +9039,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125721492</v>
+        <v>125720225</v>
       </c>
       <c r="B81" t="n">
-        <v>79009</v>
+        <v>96605</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9027,21 +9050,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9051,10 +9074,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>397334</v>
+        <v>397113</v>
       </c>
       <c r="R81" t="n">
-        <v>6697894</v>
+        <v>6697838</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9097,26 +9120,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9133,32 +9136,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125720252</v>
+        <v>125721492</v>
       </c>
       <c r="B82" t="n">
-        <v>98352</v>
+        <v>79009</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9168,10 +9171,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397108</v>
+        <v>397334</v>
       </c>
       <c r="R82" t="n">
-        <v>6697837</v>
+        <v>6697894</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9214,6 +9217,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9230,32 +9253,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125721012</v>
+        <v>125720252</v>
       </c>
       <c r="B83" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9265,10 +9288,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397124</v>
+        <v>397108</v>
       </c>
       <c r="R83" t="n">
-        <v>6697850</v>
+        <v>6697837</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9327,32 +9350,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125720843</v>
+        <v>125721012</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>80040</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9362,10 +9385,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397075</v>
+        <v>397124</v>
       </c>
       <c r="R84" t="n">
-        <v>6697869</v>
+        <v>6697850</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9424,7 +9447,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125722033</v>
+        <v>125720843</v>
       </c>
       <c r="B85" t="n">
         <v>78977</v>
@@ -9455,14 +9478,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397606</v>
+        <v>397075</v>
       </c>
       <c r="R85" t="n">
-        <v>6697859</v>
+        <v>6697869</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9521,10 +9544,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125722105</v>
+        <v>125722033</v>
       </c>
       <c r="B86" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9532,21 +9555,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9556,10 +9579,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397625</v>
+        <v>397606</v>
       </c>
       <c r="R86" t="n">
-        <v>6697852</v>
+        <v>6697859</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9602,26 +9625,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9638,45 +9641,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125720079</v>
+        <v>125722105</v>
       </c>
       <c r="B87" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397116</v>
+        <v>397625</v>
       </c>
       <c r="R87" t="n">
-        <v>6697830</v>
+        <v>6697852</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9722,22 +9725,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Betula pendula</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -9755,32 +9758,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125721614</v>
+        <v>125720079</v>
       </c>
       <c r="B88" t="n">
-        <v>78736</v>
+        <v>80040</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9790,10 +9793,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397350</v>
+        <v>397116</v>
       </c>
       <c r="R88" t="n">
-        <v>6697835</v>
+        <v>6697830</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9836,6 +9839,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -9852,10 +9875,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125721536</v>
+        <v>125721614</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9863,21 +9886,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9887,10 +9910,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397361</v>
+        <v>397350</v>
       </c>
       <c r="R89" t="n">
-        <v>6697854</v>
+        <v>6697835</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9949,10 +9972,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125721835</v>
+        <v>125721536</v>
       </c>
       <c r="B90" t="n">
-        <v>80952</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9960,34 +9983,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397433</v>
+        <v>397361</v>
       </c>
       <c r="R90" t="n">
-        <v>6697891</v>
+        <v>6697854</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10046,10 +10069,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125722112</v>
+        <v>125721835</v>
       </c>
       <c r="B91" t="n">
-        <v>78977</v>
+        <v>80952</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10057,34 +10080,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>397625</v>
+        <v>397433</v>
       </c>
       <c r="R91" t="n">
-        <v>6697852</v>
+        <v>6697891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10143,10 +10166,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125720934</v>
+        <v>125722112</v>
       </c>
       <c r="B92" t="n">
-        <v>96605</v>
+        <v>78977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10154,34 +10177,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>397112</v>
+        <v>397625</v>
       </c>
       <c r="R92" t="n">
-        <v>6697860</v>
+        <v>6697852</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10240,32 +10263,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125720473</v>
+        <v>125720934</v>
       </c>
       <c r="B93" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10275,10 +10298,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>397024</v>
+        <v>397112</v>
       </c>
       <c r="R93" t="n">
-        <v>6697840</v>
+        <v>6697860</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10337,7 +10360,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125721877</v>
+        <v>125720473</v>
       </c>
       <c r="B94" t="n">
         <v>75011</v>
@@ -10368,14 +10391,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397502</v>
+        <v>397024</v>
       </c>
       <c r="R94" t="n">
-        <v>6697866</v>
+        <v>6697840</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10434,55 +10457,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125722060</v>
+        <v>125721877</v>
       </c>
       <c r="B95" t="n">
-        <v>57816</v>
+        <v>75011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397606</v>
+        <v>397502</v>
       </c>
       <c r="R95" t="n">
-        <v>6697859</v>
+        <v>6697866</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10541,10 +10554,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125721765</v>
+        <v>125722060</v>
       </c>
       <c r="B96" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10552,34 +10565,44 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>397383</v>
+        <v>397606</v>
       </c>
       <c r="R96" t="n">
-        <v>6697865</v>
+        <v>6697859</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10638,54 +10661,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125720910</v>
+        <v>125721765</v>
       </c>
       <c r="B97" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>397092</v>
+        <v>397383</v>
       </c>
       <c r="R97" t="n">
-        <v>6697872</v>
+        <v>6697865</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10744,45 +10758,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125720604</v>
+        <v>125720910</v>
       </c>
       <c r="B98" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>396991</v>
+        <v>397092</v>
       </c>
       <c r="R98" t="n">
-        <v>6697837</v>
+        <v>6697872</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10841,10 +10864,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125721651</v>
+        <v>125720604</v>
       </c>
       <c r="B99" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10852,21 +10875,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10876,10 +10899,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>397346</v>
+        <v>396991</v>
       </c>
       <c r="R99" t="n">
-        <v>6697842</v>
+        <v>6697837</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10938,7 +10961,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721224</v>
+        <v>125721651</v>
       </c>
       <c r="B100" t="n">
         <v>78977</v>
@@ -10973,10 +10996,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397232</v>
+        <v>397346</v>
       </c>
       <c r="R100" t="n">
-        <v>6697857</v>
+        <v>6697842</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11035,10 +11058,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125721700</v>
+        <v>125721224</v>
       </c>
       <c r="B101" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11046,21 +11069,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11070,10 +11093,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397397</v>
+        <v>397232</v>
       </c>
       <c r="R101" t="n">
-        <v>6697850</v>
+        <v>6697857</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11132,10 +11155,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125720121</v>
+        <v>125721700</v>
       </c>
       <c r="B102" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11143,21 +11166,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11167,10 +11190,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>397116</v>
+        <v>397397</v>
       </c>
       <c r="R102" t="n">
-        <v>6697806</v>
+        <v>6697850</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11205,11 +11228,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11218,26 +11236,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11254,54 +11252,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125720782</v>
+        <v>125720121</v>
       </c>
       <c r="B103" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>397014</v>
+        <v>397116</v>
       </c>
       <c r="R103" t="n">
-        <v>6697845</v>
+        <v>6697806</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11336,6 +11325,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11344,6 +11338,26 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11360,45 +11374,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125720994</v>
+        <v>125720782</v>
       </c>
       <c r="B104" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>397124</v>
+        <v>397014</v>
       </c>
       <c r="R104" t="n">
-        <v>6697850</v>
+        <v>6697845</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11433,11 +11456,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11446,26 +11464,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11482,10 +11480,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125721374</v>
+        <v>125720994</v>
       </c>
       <c r="B105" t="n">
-        <v>79595</v>
+        <v>80080</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11493,21 +11491,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11517,10 +11515,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>397266</v>
+        <v>397124</v>
       </c>
       <c r="R105" t="n">
-        <v>6697866</v>
+        <v>6697850</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,6 +11553,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -11563,6 +11566,26 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11579,10 +11602,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125720024</v>
+        <v>125721374</v>
       </c>
       <c r="B106" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11590,21 +11613,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11614,13 +11637,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>397180</v>
+        <v>397266</v>
       </c>
       <c r="R106" t="n">
-        <v>6697817</v>
+        <v>6697866</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11647,19 +11670,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>18:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11674,22 +11687,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126608319</v>
+        <v>125720024</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>78977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11717,17 +11730,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>397411</v>
+        <v>397180</v>
       </c>
       <c r="R107" t="n">
-        <v>6697838</v>
+        <v>6697817</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11751,22 +11764,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11781,15 +11794,122 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126608319</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>397411</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6697838</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
           <t>Maja Larsson</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
+      <c r="AX108" t="inlineStr">
         <is>
           <t>Maja Larsson</t>
         </is>
       </c>
-      <c r="AY107" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7766,7 +7766,7 @@
         <v>125419408</v>
       </c>
       <c r="B69" t="n">
-        <v>75080</v>
+        <v>75073</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>125419873</v>
       </c>
       <c r="B70" t="n">
-        <v>79042</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>125419887</v>
       </c>
       <c r="B71" t="n">
-        <v>75080</v>
+        <v>75073</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>125419637</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8200,62 +8200,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129922856</v>
+        <v>130013052</v>
       </c>
       <c r="B73" t="n">
-        <v>98833</v>
+        <v>80285</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>397909</v>
+        <v>398130</v>
       </c>
       <c r="R73" t="n">
-        <v>6697934</v>
+        <v>6697932</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8277,19 +8263,14 @@
           <t>Norra Ny</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>S-Tor-0391</t>
-        </is>
-      </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8304,64 +8285,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130013052</v>
+        <v>125719981</v>
       </c>
       <c r="B74" t="n">
-        <v>80200</v>
+        <v>75011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>398130</v>
+        <v>397142</v>
       </c>
       <c r="R74" t="n">
-        <v>6697932</v>
+        <v>6697816</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8385,12 +8362,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8405,57 +8382,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125719981</v>
+        <v>125721868</v>
       </c>
       <c r="B75" t="n">
-        <v>75011</v>
+        <v>91242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>397142</v>
+        <v>397473</v>
       </c>
       <c r="R75" t="n">
-        <v>6697816</v>
+        <v>6697852</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8514,10 +8491,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125721868</v>
+        <v>125721577</v>
       </c>
       <c r="B76" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8525,34 +8502,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>397473</v>
+        <v>397395</v>
       </c>
       <c r="R76" t="n">
-        <v>6697852</v>
+        <v>6697867</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8595,6 +8572,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8611,10 +8608,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125721577</v>
+        <v>125721710</v>
       </c>
       <c r="B77" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8622,21 +8619,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8646,10 +8643,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>397395</v>
+        <v>397381</v>
       </c>
       <c r="R77" t="n">
-        <v>6697867</v>
+        <v>6697850</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8692,26 +8689,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8728,32 +8705,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125721710</v>
+        <v>125721040</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>75011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8763,10 +8740,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>397381</v>
+        <v>397171</v>
       </c>
       <c r="R78" t="n">
-        <v>6697850</v>
+        <v>6697871</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8825,32 +8802,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125721040</v>
+        <v>125719936</v>
       </c>
       <c r="B79" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8860,10 +8837,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>397171</v>
+        <v>397145</v>
       </c>
       <c r="R79" t="n">
-        <v>6697871</v>
+        <v>6697801</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8906,6 +8883,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8922,7 +8919,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125719936</v>
+        <v>125720225</v>
       </c>
       <c r="B80" t="n">
         <v>96605</v>
@@ -8957,10 +8954,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>397145</v>
+        <v>397113</v>
       </c>
       <c r="R80" t="n">
-        <v>6697801</v>
+        <v>6697838</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9003,26 +9000,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9039,10 +9016,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125720225</v>
+        <v>125721492</v>
       </c>
       <c r="B81" t="n">
-        <v>96605</v>
+        <v>79009</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9050,21 +9027,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9074,10 +9051,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>397113</v>
+        <v>397334</v>
       </c>
       <c r="R81" t="n">
-        <v>6697838</v>
+        <v>6697894</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9120,6 +9097,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9136,32 +9133,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125721492</v>
+        <v>125720252</v>
       </c>
       <c r="B82" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9171,10 +9168,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>397334</v>
+        <v>397108</v>
       </c>
       <c r="R82" t="n">
-        <v>6697894</v>
+        <v>6697837</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9217,26 +9214,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pendula</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9253,32 +9230,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125720252</v>
+        <v>125721012</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>80040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9288,10 +9265,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>397108</v>
+        <v>397124</v>
       </c>
       <c r="R83" t="n">
-        <v>6697837</v>
+        <v>6697850</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9350,32 +9327,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125721012</v>
+        <v>125720843</v>
       </c>
       <c r="B84" t="n">
-        <v>80040</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9385,10 +9362,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>397124</v>
+        <v>397075</v>
       </c>
       <c r="R84" t="n">
-        <v>6697850</v>
+        <v>6697869</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9447,7 +9424,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125720843</v>
+        <v>125722033</v>
       </c>
       <c r="B85" t="n">
         <v>78977</v>
@@ -9478,14 +9455,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>397075</v>
+        <v>397606</v>
       </c>
       <c r="R85" t="n">
-        <v>6697869</v>
+        <v>6697859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9544,10 +9521,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125722033</v>
+        <v>125722105</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9555,21 +9532,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9579,10 +9556,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>397606</v>
+        <v>397625</v>
       </c>
       <c r="R86" t="n">
-        <v>6697859</v>
+        <v>6697852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9625,6 +9602,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pendula</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9641,45 +9638,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125722105</v>
+        <v>125720079</v>
       </c>
       <c r="B87" t="n">
-        <v>80080</v>
+        <v>80040</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>397625</v>
+        <v>397116</v>
       </c>
       <c r="R87" t="n">
-        <v>6697852</v>
+        <v>6697830</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9725,22 +9722,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula pendula</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -9758,32 +9755,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125720079</v>
+        <v>125721614</v>
       </c>
       <c r="B88" t="n">
-        <v>80040</v>
+        <v>78736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9793,10 +9790,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>397116</v>
+        <v>397350</v>
       </c>
       <c r="R88" t="n">
-        <v>6697830</v>
+        <v>6697835</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9839,26 +9836,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -9875,10 +9852,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125721614</v>
+        <v>125721536</v>
       </c>
       <c r="B89" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9886,21 +9863,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9910,10 +9887,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>397350</v>
+        <v>397361</v>
       </c>
       <c r="R89" t="n">
-        <v>6697835</v>
+        <v>6697854</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9972,10 +9949,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125721536</v>
+        <v>125721835</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>80952</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9983,34 +9960,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>397361</v>
+        <v>397433</v>
       </c>
       <c r="R90" t="n">
-        <v>6697854</v>
+        <v>6697891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10069,10 +10046,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125721835</v>
+        <v>125722112</v>
       </c>
       <c r="B91" t="n">
-        <v>80952</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10080,34 +10057,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>397433</v>
+        <v>397625</v>
       </c>
       <c r="R91" t="n">
-        <v>6697891</v>
+        <v>6697852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10166,10 +10143,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125722112</v>
+        <v>125720934</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>96605</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10177,34 +10154,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>397625</v>
+        <v>397112</v>
       </c>
       <c r="R92" t="n">
-        <v>6697852</v>
+        <v>6697860</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10263,32 +10240,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125720934</v>
+        <v>125720473</v>
       </c>
       <c r="B93" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10298,10 +10275,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>397112</v>
+        <v>397024</v>
       </c>
       <c r="R93" t="n">
-        <v>6697860</v>
+        <v>6697840</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10360,7 +10337,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125720473</v>
+        <v>125721877</v>
       </c>
       <c r="B94" t="n">
         <v>75011</v>
@@ -10391,14 +10368,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>397024</v>
+        <v>397502</v>
       </c>
       <c r="R94" t="n">
-        <v>6697840</v>
+        <v>6697866</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10457,45 +10434,55 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125721877</v>
+        <v>125722060</v>
       </c>
       <c r="B95" t="n">
-        <v>75011</v>
+        <v>57816</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>397502</v>
+        <v>397606</v>
       </c>
       <c r="R95" t="n">
-        <v>6697866</v>
+        <v>6697859</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10554,10 +10541,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125722060</v>
+        <v>125721765</v>
       </c>
       <c r="B96" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10565,44 +10552,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>397606</v>
+        <v>397383</v>
       </c>
       <c r="R96" t="n">
-        <v>6697859</v>
+        <v>6697865</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10661,45 +10638,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125721765</v>
+        <v>125720910</v>
       </c>
       <c r="B97" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>397383</v>
+        <v>397092</v>
       </c>
       <c r="R97" t="n">
-        <v>6697865</v>
+        <v>6697872</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10758,54 +10744,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125720910</v>
+        <v>125720604</v>
       </c>
       <c r="B98" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>397092</v>
+        <v>396991</v>
       </c>
       <c r="R98" t="n">
-        <v>6697872</v>
+        <v>6697837</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10864,10 +10841,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125720604</v>
+        <v>125721651</v>
       </c>
       <c r="B99" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10875,21 +10852,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10899,10 +10876,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>396991</v>
+        <v>397346</v>
       </c>
       <c r="R99" t="n">
-        <v>6697837</v>
+        <v>6697842</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10961,7 +10938,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125721651</v>
+        <v>125721224</v>
       </c>
       <c r="B100" t="n">
         <v>78977</v>
@@ -10996,10 +10973,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>397346</v>
+        <v>397232</v>
       </c>
       <c r="R100" t="n">
-        <v>6697842</v>
+        <v>6697857</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11058,10 +11035,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125721224</v>
+        <v>125721700</v>
       </c>
       <c r="B101" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11069,21 +11046,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11093,10 +11070,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>397232</v>
+        <v>397397</v>
       </c>
       <c r="R101" t="n">
-        <v>6697857</v>
+        <v>6697850</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11155,10 +11132,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125721700</v>
+        <v>125720121</v>
       </c>
       <c r="B102" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11166,21 +11143,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11190,10 +11167,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>397397</v>
+        <v>397116</v>
       </c>
       <c r="R102" t="n">
-        <v>6697850</v>
+        <v>6697806</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11228,6 +11205,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Intill en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11236,6 +11218,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11252,45 +11254,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125720121</v>
+        <v>125720782</v>
       </c>
       <c r="B103" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>397116</v>
+        <v>397014</v>
       </c>
       <c r="R103" t="n">
-        <v>6697806</v>
+        <v>6697845</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11325,11 +11336,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Intill en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11338,26 +11344,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11374,54 +11360,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125720782</v>
+        <v>125720994</v>
       </c>
       <c r="B104" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>397014</v>
+        <v>397124</v>
       </c>
       <c r="R104" t="n">
-        <v>6697845</v>
+        <v>6697850</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11456,6 +11433,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>200-årig asp.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -11464,6 +11446,26 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11480,10 +11482,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125720994</v>
+        <v>125721374</v>
       </c>
       <c r="B105" t="n">
-        <v>80080</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11491,21 +11493,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11515,10 +11517,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>397124</v>
+        <v>397266</v>
       </c>
       <c r="R105" t="n">
-        <v>6697850</v>
+        <v>6697866</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11553,11 +11555,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>200-årig asp.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -11566,26 +11563,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11602,10 +11579,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125721374</v>
+        <v>125720024</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11613,21 +11590,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11637,13 +11614,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>397266</v>
+        <v>397180</v>
       </c>
       <c r="R106" t="n">
-        <v>6697866</v>
+        <v>6697817</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11670,9 +11647,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11687,22 +11674,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125720024</v>
+        <v>126608319</v>
       </c>
       <c r="B107" t="n">
-        <v>78977</v>
+        <v>79011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11730,17 +11717,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Klingelmyren, Klingelmyren, Vrm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>397180</v>
+        <v>397411</v>
       </c>
       <c r="R107" t="n">
-        <v>6697817</v>
+        <v>6697838</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11764,22 +11751,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11794,122 +11781,15 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Maja Larsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Maja Larsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>126608319</v>
-      </c>
-      <c r="B108" t="n">
-        <v>79014</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Klingelmyren, Klingelmyren, Vrm</t>
-        </is>
-      </c>
-      <c r="Q108" t="n">
-        <v>397411</v>
-      </c>
-      <c r="R108" t="n">
-        <v>6697838</v>
-      </c>
-      <c r="S108" t="n">
-        <v>10</v>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>Norra Ny</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AD108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="inlineStr"/>
-      <c r="AW108" t="inlineStr">
-        <is>
-          <t>Maja Larsson</t>
-        </is>
-      </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>Maja Larsson</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61021-2024 artfynd.xlsx
+++ b/artfynd/A 61021-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AZ145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700601</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105046</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105179</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105079</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105023</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125722291</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105486</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104243</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105360</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125696883</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419090</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,6 +2048,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419405</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125447044</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125447089</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2302,6 +2382,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125697120</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2399,6 +2484,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700680</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104363</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419507</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,6 +2810,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125696949</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2817,6 +2922,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120106227</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125697091</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3031,6 +3146,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700564</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3157,6 +3277,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419300</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3272,6 +3397,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419158</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3374,6 +3504,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125722311</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3481,6 +3616,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104728</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3593,6 +3733,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419083</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3700,6 +3845,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120104244</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3797,6 +3947,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120107461</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3918,6 +4073,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426785</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4039,6 +4199,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426865</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4145,6 +4310,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125696921</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4251,6 +4421,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125697063</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4348,6 +4523,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105969</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4455,6 +4635,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419514</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4557,6 +4742,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385073</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4659,6 +4849,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385044</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4761,6 +4956,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385075</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4858,6 +5058,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125697625</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4955,6 +5160,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700092</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5057,6 +5267,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385057</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5160,6 +5375,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385064</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5262,6 +5482,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385072</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5364,6 +5589,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385076</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5471,6 +5701,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125425539</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5568,6 +5803,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698993</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5670,6 +5910,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385052</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5772,6 +6017,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385070</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5874,6 +6124,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385071</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5981,6 +6236,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125418813</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6088,6 +6348,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419540</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6195,6 +6460,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419637</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6302,6 +6572,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419996</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6409,6 +6684,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420150</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6516,6 +6796,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125425042</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6613,6 +6898,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125697394</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6710,6 +7000,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698253</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6807,6 +7102,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698508</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6904,6 +7204,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698527</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7001,6 +7306,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698599</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7098,6 +7408,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698761</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7195,6 +7510,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698905</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7292,6 +7612,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699011</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7389,6 +7714,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699640</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7486,6 +7816,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699719</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7583,6 +7918,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699772</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7680,6 +8020,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699868</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7777,6 +8122,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700252</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7874,6 +8224,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700296</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7971,6 +8326,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700356</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8073,6 +8433,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385054</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8175,6 +8540,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385058</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8277,6 +8647,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385059</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8379,6 +8754,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385061</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8481,6 +8861,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385062</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8583,6 +8968,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385066</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8685,6 +9075,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385067</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8787,6 +9182,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385069</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8903,6 +9303,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419081</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9010,6 +9415,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419719</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9117,6 +9527,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419887</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9224,6 +9639,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419993</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9331,6 +9751,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125422828</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9438,6 +9863,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426528</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9535,6 +9965,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125697246</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9632,6 +10067,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698845</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9729,6 +10169,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700176</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9826,6 +10271,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700228</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9923,6 +10373,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125700268</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10030,6 +10485,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419675</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10146,6 +10606,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419873</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10257,6 +10722,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420220</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10354,6 +10824,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698924</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10456,6 +10931,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385056</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10558,6 +11038,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86385043</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10697,6 +11182,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122377554</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10794,6 +11284,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013052</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10909,6 +11404,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125425047</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11011,6 +11511,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698310</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11113,6 +11618,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698359</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11215,6 +11725,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698575</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11317,6 +11832,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698646</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11419,6 +11939,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125698710</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11545,6 +12070,11 @@
           <t>Inventering av raggbock och dess livsmiljöer</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70371756</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11674,6 +12204,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122377425</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11780,6 +12315,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699923</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11887,6 +12427,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125425784</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11998,6 +12543,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125419626</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12115,6 +12665,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125719936</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12222,6 +12777,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720024</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12319,6 +12879,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125719981</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12441,6 +13006,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720121</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12567,6 +13137,11 @@
           <t>Inventering av raggbock och dess livsmiljöer</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70372212</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12664,6 +13239,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720225</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12761,6 +13341,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720934</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12878,6 +13463,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721492</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12975,6 +13565,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721835</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13072,6 +13667,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720604</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13169,6 +13769,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721868</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13266,6 +13871,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720843</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13363,6 +13973,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721224</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13460,6 +14075,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721536</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13557,6 +14177,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721651</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13654,6 +14279,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721710</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13751,6 +14381,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721765</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13848,6 +14483,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125722033</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13945,6 +14585,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125722112</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14052,6 +14697,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608319</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14149,6 +14799,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720473</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14246,6 +14901,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721040</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14343,6 +15003,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721877</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14440,6 +15105,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721700</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14537,6 +15207,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721374</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14659,6 +15334,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720994</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14776,6 +15456,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721577</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14893,6 +15578,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125722105</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15000,6 +15690,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125722060</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15097,6 +15792,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720252</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15203,6 +15903,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720782</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15309,6 +16014,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720910</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15406,6 +16116,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721614</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15523,6 +16238,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125720079</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15620,8 +16340,159 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125721012</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>